--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE38EC1B-D417-4CCE-81EC-B4DAC71A17B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A664EB-5D16-4792-802C-1C460ABE2F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="78">
   <si>
     <t>VNSH01</t>
   </si>
@@ -254,9 +254,6 @@
     <t>ĐL Dũng Thu</t>
   </si>
   <si>
-    <t>Đã trả (27/02/26)</t>
-  </si>
-  <si>
     <t>Mắt camera</t>
   </si>
   <si>
@@ -264,6 +261,15 @@
   </si>
   <si>
     <t>Chuyển qua tháng 03/2026</t>
+  </si>
+  <si>
+    <t>Chuyển qua tháng 03/2026, 20 VNSH01 đã trả</t>
+  </si>
+  <si>
+    <t>SEA</t>
+  </si>
+  <si>
+    <t>dlrantai</t>
   </si>
 </sst>
 </file>
@@ -528,9 +534,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -538,6 +541,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -593,12 +599,12 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="F3">
-            <v>22</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="4">
           <cell r="F4">
-            <v>94</v>
+            <v>120</v>
           </cell>
         </row>
         <row r="5">
@@ -697,11 +703,11 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1030,7 +1036,7 @@
       </c>
       <c r="C3" s="3">
         <f>'[1]Nhập xuất tồn'!F3</f>
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3">
         <f>Nhập!AH3</f>
@@ -1042,14 +1048,14 @@
       </c>
       <c r="F3" s="3">
         <f>C3+D3-E3</f>
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G3" s="4">
         <v>1</v>
       </c>
       <c r="H3" s="3">
         <f>F3-G3</f>
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1061,11 +1067,11 @@
       </c>
       <c r="C4" s="3">
         <f>'[1]Nhập xuất tồn'!F4</f>
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="D4" s="3">
         <f>Nhập!AH4</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E4" s="3">
         <f>Xuất!AH5+Huỷ!AH4</f>
@@ -1073,14 +1079,14 @@
       </c>
       <c r="F4" s="3">
         <f>C4+D4-E4</f>
-        <v>94</v>
+        <v>192</v>
       </c>
       <c r="G4" s="4">
         <v>16</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" ref="H4:H22" si="0">F4-G4</f>
-        <v>78</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1638,7 +1644,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C23" s="3">
         <f>'[1]Nhập xuất tồn'!F23</f>
@@ -1669,11 +1675,11 @@
       <c r="B24" s="26"/>
       <c r="C24" s="3">
         <f>SUM(C3:C22)</f>
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D24" s="3">
         <f t="shared" ref="D24:G24" si="2">SUM(D3:D22)</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
@@ -1681,7 +1687,7 @@
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>130</v>
+        <v>208</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
@@ -1689,7 +1695,7 @@
       </c>
       <c r="H24" s="3">
         <f>SUM(H3:H23)</f>
-        <v>112</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1924,7 +1930,9 @@
         <v>1</v>
       </c>
       <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="D4" s="5">
+        <v>72</v>
+      </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
@@ -1956,7 +1964,7 @@
       <c r="AG4" s="5"/>
       <c r="AH4" s="5">
         <f t="shared" ref="AH4:AH19" si="0">SUM(C4:AG4)</f>
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
@@ -2723,7 +2731,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -3812,7 +3820,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -4905,7 +4913,7 @@
       <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="32">
+      <c r="A2" s="35">
         <v>46055</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -4922,7 +4930,7 @@
       <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="32"/>
+      <c r="A3" s="35"/>
       <c r="B3" s="15" t="s">
         <v>40</v>
       </c>
@@ -4937,7 +4945,7 @@
       <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="32"/>
+      <c r="A4" s="35"/>
       <c r="B4" s="15" t="s">
         <v>41</v>
       </c>
@@ -4952,7 +4960,7 @@
       <c r="G4" s="16"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="32"/>
+      <c r="A5" s="35"/>
       <c r="B5" s="15" t="s">
         <v>42</v>
       </c>
@@ -4967,7 +4975,7 @@
       <c r="G5" s="16"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="32">
+      <c r="A6" s="35">
         <v>46056</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -4984,7 +4992,7 @@
       <c r="G6" s="16"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="32"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="15" t="s">
         <v>44</v>
       </c>
@@ -4999,7 +5007,7 @@
       <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="32">
+      <c r="A8" s="35">
         <v>46057</v>
       </c>
       <c r="B8" s="14" t="s">
@@ -5016,7 +5024,7 @@
       <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="32"/>
+      <c r="A9" s="35"/>
       <c r="B9" s="15" t="s">
         <v>40</v>
       </c>
@@ -5031,7 +5039,7 @@
       <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
+      <c r="A10" s="35">
         <v>46058</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -5048,7 +5056,7 @@
       <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="32"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="15" t="s">
         <v>50</v>
       </c>
@@ -5063,7 +5071,7 @@
       <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="32">
+      <c r="A12" s="35">
         <v>46059</v>
       </c>
       <c r="B12" s="15" t="s">
@@ -5080,7 +5088,7 @@
       <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="32"/>
+      <c r="A13" s="35"/>
       <c r="B13" s="15" t="s">
         <v>51</v>
       </c>
@@ -5112,7 +5120,7 @@
       <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="32">
+      <c r="A15" s="35">
         <v>46062</v>
       </c>
       <c r="B15" s="15" t="s">
@@ -5129,7 +5137,7 @@
       <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="32"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="15" t="s">
         <v>42</v>
       </c>
@@ -5178,7 +5186,7 @@
       <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="32">
+      <c r="A19" s="35">
         <v>46065</v>
       </c>
       <c r="B19" s="15" t="s">
@@ -5195,7 +5203,7 @@
       <c r="G19" s="16"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="32"/>
+      <c r="A20" s="35"/>
       <c r="B20" s="15" t="s">
         <v>50</v>
       </c>
@@ -5210,7 +5218,7 @@
       <c r="G20" s="16"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="33">
+      <c r="A21" s="32">
         <v>46076</v>
       </c>
       <c r="B21" s="15" t="s">
@@ -5227,7 +5235,7 @@
       <c r="G21" s="16"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="35"/>
+      <c r="A22" s="34"/>
       <c r="B22" s="15" t="s">
         <v>65</v>
       </c>
@@ -5242,7 +5250,7 @@
       <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="34"/>
+      <c r="A23" s="33"/>
       <c r="B23" s="15" t="s">
         <v>67</v>
       </c>
@@ -5257,7 +5265,7 @@
       <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="33">
+      <c r="A24" s="32">
         <v>46077</v>
       </c>
       <c r="B24" s="15" t="s">
@@ -5274,7 +5282,7 @@
       <c r="G24" s="16"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="35"/>
+      <c r="A25" s="34"/>
       <c r="B25" s="15" t="s">
         <v>64</v>
       </c>
@@ -5289,7 +5297,7 @@
       <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="34"/>
+      <c r="A26" s="33"/>
       <c r="B26" s="15" t="s">
         <v>14</v>
       </c>
@@ -5303,8 +5311,8 @@
       </c>
       <c r="G26" s="16"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="33">
+    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="32">
         <v>46078</v>
       </c>
       <c r="B27" s="15" t="s">
@@ -5325,7 +5333,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
+      <c r="A28" s="33"/>
       <c r="B28" s="15" t="s">
         <v>50</v>
       </c>
@@ -5340,7 +5348,7 @@
       <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="33">
+      <c r="A29" s="32">
         <v>46079</v>
       </c>
       <c r="B29" s="15" t="s">
@@ -5359,7 +5367,7 @@
       <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="35"/>
+      <c r="A30" s="34"/>
       <c r="B30" s="15" t="s">
         <v>71</v>
       </c>
@@ -5374,7 +5382,7 @@
       <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="34"/>
+      <c r="A31" s="33"/>
       <c r="B31" s="15" t="s">
         <v>50</v>
       </c>
@@ -5384,7 +5392,7 @@
         <v>20</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G31" s="16"/>
     </row>
@@ -5404,52 +5412,84 @@
         <v>69</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="14"/>
-      <c r="B33" s="15"/>
+      <c r="A33" s="32">
+        <v>46083</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>48</v>
+      </c>
       <c r="C33" s="15"/>
       <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
+      <c r="E33" s="15">
+        <v>10</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>69</v>
+      </c>
       <c r="G33" s="16"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="14"/>
-      <c r="B34" s="15"/>
+      <c r="A34" s="34"/>
+      <c r="B34" s="15" t="s">
+        <v>50</v>
+      </c>
       <c r="C34" s="15"/>
       <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
+      <c r="E34" s="15">
+        <v>10</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>69</v>
+      </c>
       <c r="G34" s="16"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="14"/>
-      <c r="B35" s="15"/>
+      <c r="A35" s="34"/>
+      <c r="B35" s="15" t="s">
+        <v>14</v>
+      </c>
       <c r="C35" s="15"/>
       <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
+      <c r="E35" s="15">
+        <v>2</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>69</v>
+      </c>
       <c r="G35" s="16"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="14"/>
-      <c r="B36" s="15"/>
+      <c r="A36" s="34"/>
+      <c r="B36" s="15" t="s">
+        <v>76</v>
+      </c>
       <c r="C36" s="15"/>
       <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
+      <c r="E36" s="15">
+        <v>30</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>69</v>
+      </c>
       <c r="G36" s="16"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="14"/>
-      <c r="B37" s="15"/>
+      <c r="A37" s="33"/>
+      <c r="B37" s="15" t="s">
+        <v>77</v>
+      </c>
       <c r="C37" s="15"/>
       <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
+      <c r="E37" s="15">
+        <v>1</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>69</v>
+      </c>
       <c r="G37" s="16"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -5572,18 +5612,19 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F7" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
-  <mergeCells count="11">
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A29:A31"/>
+  <mergeCells count="12">
+    <mergeCell ref="A33:A37"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A29:A31"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:F1000">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -5655,7 +5696,7 @@
       </c>
       <c r="C3" s="3">
         <f>SUM('Nhập xuất tồn'!C3)</f>
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3">
         <f>SUM('Nhập xuất tồn'!D3)</f>
@@ -5667,14 +5708,14 @@
       </c>
       <c r="F3" s="3">
         <f>SUM(C3+D3-E3)</f>
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G3" s="4">
         <v>1</v>
       </c>
       <c r="H3" s="3">
         <f>SUM(F3-G3)</f>
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -5686,11 +5727,11 @@
       </c>
       <c r="C4" s="3">
         <f>SUM('Nhập xuất tồn'!C4)</f>
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="D4" s="3">
         <f>SUM('Nhập xuất tồn'!D4)</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E4" s="3">
         <f>SUM('Nhập xuất tồn'!E4)</f>
@@ -5698,14 +5739,14 @@
       </c>
       <c r="F4" s="3">
         <f>SUM(C4+D4-E4)</f>
-        <v>94</v>
+        <v>192</v>
       </c>
       <c r="G4" s="4">
         <v>14</v>
       </c>
       <c r="H4" s="3">
         <f>SUM(F4-G4)</f>
-        <v>80</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -6106,7 +6147,7 @@
         <v>21</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C18" s="3">
         <f>'Nhập xuất tồn'!C23</f>
@@ -6140,11 +6181,11 @@
       <c r="B19" s="36"/>
       <c r="C19" s="10">
         <f>SUM(C3:C17)</f>
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D19" s="10">
         <f>SUM(D3:D17)</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E19" s="10">
         <f>SUM(E3:E17)</f>
@@ -6152,7 +6193,7 @@
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>130</v>
+        <v>208</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
@@ -6160,7 +6201,7 @@
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>115</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A664EB-5D16-4792-802C-1C460ABE2F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85FBCED9-1138-4597-BA27-FCCD753158AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="79">
   <si>
     <t>VNSH01</t>
   </si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>dlrantai</t>
+  </si>
+  <si>
+    <t>Đã trả (02/03/26)</t>
   </si>
 </sst>
 </file>
@@ -537,10 +540,10 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1075,18 +1078,18 @@
       </c>
       <c r="E4" s="3">
         <f>Xuất!AH5+Huỷ!AH4</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" s="3">
         <f>C4+D4-E4</f>
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G4" s="4">
         <v>16</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" ref="H4:H22" si="0">F4-G4</f>
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1683,11 +1686,11 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
@@ -1695,7 +1698,7 @@
       </c>
       <c r="H24" s="3">
         <f>SUM(H3:H23)</f>
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -3021,7 +3024,9 @@
         <v>1</v>
       </c>
       <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="D5" s="5">
+        <v>3</v>
+      </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -3053,7 +3058,7 @@
       <c r="AG5" s="5"/>
       <c r="AH5" s="5">
         <f t="shared" ref="AH5:AH18" si="0">SUM(C5:AG5)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
@@ -5235,7 +5240,7 @@
       <c r="G21" s="16"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
+      <c r="A22" s="33"/>
       <c r="B22" s="15" t="s">
         <v>65</v>
       </c>
@@ -5250,7 +5255,7 @@
       <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="33"/>
+      <c r="A23" s="34"/>
       <c r="B23" s="15" t="s">
         <v>67</v>
       </c>
@@ -5282,7 +5287,7 @@
       <c r="G24" s="16"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="34"/>
+      <c r="A25" s="33"/>
       <c r="B25" s="15" t="s">
         <v>64</v>
       </c>
@@ -5297,7 +5302,7 @@
       <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="33"/>
+      <c r="A26" s="34"/>
       <c r="B26" s="15" t="s">
         <v>14</v>
       </c>
@@ -5333,7 +5338,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="33"/>
+      <c r="A28" s="34"/>
       <c r="B28" s="15" t="s">
         <v>50</v>
       </c>
@@ -5367,7 +5372,7 @@
       <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="34"/>
+      <c r="A30" s="33"/>
       <c r="B30" s="15" t="s">
         <v>71</v>
       </c>
@@ -5382,7 +5387,7 @@
       <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="33"/>
+      <c r="A31" s="34"/>
       <c r="B31" s="15" t="s">
         <v>50</v>
       </c>
@@ -5433,7 +5438,7 @@
       <c r="G33" s="16"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="34"/>
+      <c r="A34" s="33"/>
       <c r="B34" s="15" t="s">
         <v>50</v>
       </c>
@@ -5448,7 +5453,7 @@
       <c r="G34" s="16"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="34"/>
+      <c r="A35" s="33"/>
       <c r="B35" s="15" t="s">
         <v>14</v>
       </c>
@@ -5458,12 +5463,12 @@
         <v>2</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G35" s="16"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="34"/>
+      <c r="A36" s="33"/>
       <c r="B36" s="15" t="s">
         <v>76</v>
       </c>
@@ -5488,17 +5493,23 @@
         <v>1</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G37" s="16"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="14"/>
-      <c r="B38" s="15"/>
+      <c r="A38" s="34"/>
+      <c r="B38" s="15" t="s">
+        <v>62</v>
+      </c>
       <c r="C38" s="15"/>
       <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
+      <c r="E38" s="15">
+        <v>50</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>69</v>
+      </c>
       <c r="G38" s="16"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -5613,7 +5624,6 @@
   </sheetData>
   <autoFilter ref="A1:F7" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
   <mergeCells count="12">
-    <mergeCell ref="A33:A37"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
@@ -5625,6 +5635,7 @@
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A33:A38"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:F1000">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -5735,18 +5746,18 @@
       </c>
       <c r="E4" s="3">
         <f>SUM('Nhập xuất tồn'!E4)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" s="3">
         <f>SUM(C4+D4-E4)</f>
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G4" s="4">
         <v>14</v>
       </c>
       <c r="H4" s="3">
         <f>SUM(F4-G4)</f>
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -6189,11 +6200,11 @@
       </c>
       <c r="E19" s="10">
         <f>SUM(E3:E17)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
@@ -6201,7 +6212,7 @@
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85FBCED9-1138-4597-BA27-FCCD753158AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760CD15F-E414-4B45-99A5-AA1AD9AB9D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ghi chú'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ghi chú'!$A$1:$F$38</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="81">
   <si>
     <t>VNSH01</t>
   </si>
@@ -273,6 +273,12 @@
   </si>
   <si>
     <t>Đã trả (02/03/26)</t>
+  </si>
+  <si>
+    <t>Đã trả 18 VNSH02</t>
+  </si>
+  <si>
+    <t>Đã trả (03/03/26)</t>
   </si>
 </sst>
 </file>
@@ -537,6 +543,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -544,9 +553,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -607,7 +613,7 @@
         </row>
         <row r="4">
           <cell r="F4">
-            <v>120</v>
+            <v>121</v>
           </cell>
         </row>
         <row r="5">
@@ -706,11 +712,11 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1043,7 +1049,7 @@
       </c>
       <c r="D3" s="3">
         <f>Nhập!AH3</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E3" s="3">
         <f>Xuất!AH4+Huỷ!AH3</f>
@@ -1051,14 +1057,14 @@
       </c>
       <c r="F3" s="3">
         <f>C3+D3-E3</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G3" s="4">
         <v>1</v>
       </c>
       <c r="H3" s="3">
         <f>F3-G3</f>
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1070,26 +1076,26 @@
       </c>
       <c r="C4" s="3">
         <f>'[1]Nhập xuất tồn'!F4</f>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D4" s="3">
         <f>Nhập!AH4</f>
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="E4" s="3">
         <f>Xuất!AH5+Huỷ!AH4</f>
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="F4" s="3">
         <f>C4+D4-E4</f>
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="G4" s="4">
         <v>16</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" ref="H4:H22" si="0">F4-G4</f>
-        <v>173</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1678,19 +1684,19 @@
       <c r="B24" s="26"/>
       <c r="C24" s="3">
         <f>SUM(C3:C22)</f>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D24" s="3">
         <f t="shared" ref="D24:G24" si="2">SUM(D3:D22)</f>
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
@@ -1698,7 +1704,7 @@
       </c>
       <c r="H24" s="3">
         <f>SUM(H3:H23)</f>
-        <v>187</v>
+        <v>225</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1891,7 +1897,9 @@
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
+      <c r="E3" s="5">
+        <v>8</v>
+      </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
@@ -1922,7 +1930,7 @@
       <c r="AG3" s="5"/>
       <c r="AH3" s="5">
         <f>SUM(C3:AG3)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
@@ -1936,7 +1944,9 @@
       <c r="D4" s="5">
         <v>72</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="5">
+        <v>104</v>
+      </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -1967,7 +1977,7 @@
       <c r="AG4" s="5"/>
       <c r="AH4" s="5">
         <f t="shared" ref="AH4:AH19" si="0">SUM(C4:AG4)</f>
-        <v>72</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
@@ -3027,7 +3037,9 @@
       <c r="D5" s="5">
         <v>3</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="5">
+        <v>75</v>
+      </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
@@ -3058,7 +3070,7 @@
       <c r="AG5" s="5"/>
       <c r="AH5" s="5">
         <f t="shared" ref="AH5:AH18" si="0">SUM(C5:AG5)</f>
-        <v>3</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
@@ -4918,7 +4930,7 @@
       <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="35">
+      <c r="A2" s="32">
         <v>46055</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -4935,7 +4947,7 @@
       <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="35"/>
+      <c r="A3" s="32"/>
       <c r="B3" s="15" t="s">
         <v>40</v>
       </c>
@@ -4950,7 +4962,7 @@
       <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
+      <c r="A4" s="32"/>
       <c r="B4" s="15" t="s">
         <v>41</v>
       </c>
@@ -4965,7 +4977,7 @@
       <c r="G4" s="16"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="35"/>
+      <c r="A5" s="32"/>
       <c r="B5" s="15" t="s">
         <v>42</v>
       </c>
@@ -4980,7 +4992,7 @@
       <c r="G5" s="16"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="35">
+      <c r="A6" s="32">
         <v>46056</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -4997,7 +5009,7 @@
       <c r="G6" s="16"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="35"/>
+      <c r="A7" s="32"/>
       <c r="B7" s="15" t="s">
         <v>44</v>
       </c>
@@ -5012,7 +5024,7 @@
       <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="35">
+      <c r="A8" s="32">
         <v>46057</v>
       </c>
       <c r="B8" s="14" t="s">
@@ -5029,7 +5041,7 @@
       <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="35"/>
+      <c r="A9" s="32"/>
       <c r="B9" s="15" t="s">
         <v>40</v>
       </c>
@@ -5044,7 +5056,7 @@
       <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="35">
+      <c r="A10" s="32">
         <v>46058</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -5061,7 +5073,7 @@
       <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="35"/>
+      <c r="A11" s="32"/>
       <c r="B11" s="15" t="s">
         <v>50</v>
       </c>
@@ -5076,7 +5088,7 @@
       <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="35">
+      <c r="A12" s="32">
         <v>46059</v>
       </c>
       <c r="B12" s="15" t="s">
@@ -5093,7 +5105,7 @@
       <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
+      <c r="A13" s="32"/>
       <c r="B13" s="15" t="s">
         <v>51</v>
       </c>
@@ -5125,7 +5137,7 @@
       <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="35">
+      <c r="A15" s="32">
         <v>46062</v>
       </c>
       <c r="B15" s="15" t="s">
@@ -5142,7 +5154,7 @@
       <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="35"/>
+      <c r="A16" s="32"/>
       <c r="B16" s="15" t="s">
         <v>42</v>
       </c>
@@ -5191,7 +5203,7 @@
       <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="35">
+      <c r="A19" s="32">
         <v>46065</v>
       </c>
       <c r="B19" s="15" t="s">
@@ -5208,7 +5220,7 @@
       <c r="G19" s="16"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="35"/>
+      <c r="A20" s="32"/>
       <c r="B20" s="15" t="s">
         <v>50</v>
       </c>
@@ -5223,7 +5235,7 @@
       <c r="G20" s="16"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="32">
+      <c r="A21" s="33">
         <v>46076</v>
       </c>
       <c r="B21" s="15" t="s">
@@ -5240,7 +5252,7 @@
       <c r="G21" s="16"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="33"/>
+      <c r="A22" s="34"/>
       <c r="B22" s="15" t="s">
         <v>65</v>
       </c>
@@ -5255,7 +5267,7 @@
       <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="34"/>
+      <c r="A23" s="35"/>
       <c r="B23" s="15" t="s">
         <v>67</v>
       </c>
@@ -5270,7 +5282,7 @@
       <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="32">
+      <c r="A24" s="33">
         <v>46077</v>
       </c>
       <c r="B24" s="15" t="s">
@@ -5287,7 +5299,7 @@
       <c r="G24" s="16"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="33"/>
+      <c r="A25" s="34"/>
       <c r="B25" s="15" t="s">
         <v>64</v>
       </c>
@@ -5302,7 +5314,7 @@
       <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="34"/>
+      <c r="A26" s="35"/>
       <c r="B26" s="15" t="s">
         <v>14</v>
       </c>
@@ -5317,7 +5329,7 @@
       <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="32">
+      <c r="A27" s="33">
         <v>46078</v>
       </c>
       <c r="B27" s="15" t="s">
@@ -5338,7 +5350,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
+      <c r="A28" s="35"/>
       <c r="B28" s="15" t="s">
         <v>50</v>
       </c>
@@ -5353,7 +5365,7 @@
       <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="32">
+      <c r="A29" s="33">
         <v>46079</v>
       </c>
       <c r="B29" s="15" t="s">
@@ -5372,7 +5384,7 @@
       <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="33"/>
+      <c r="A30" s="34"/>
       <c r="B30" s="15" t="s">
         <v>71</v>
       </c>
@@ -5387,7 +5399,7 @@
       <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="34"/>
+      <c r="A31" s="35"/>
       <c r="B31" s="15" t="s">
         <v>50</v>
       </c>
@@ -5414,14 +5426,14 @@
         <v>30</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="G32" s="16" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="32">
+      <c r="A33" s="33">
         <v>46083</v>
       </c>
       <c r="B33" s="15" t="s">
@@ -5433,12 +5445,12 @@
         <v>10</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="G33" s="16"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="33"/>
+      <c r="A34" s="34"/>
       <c r="B34" s="15" t="s">
         <v>50</v>
       </c>
@@ -5453,7 +5465,7 @@
       <c r="G34" s="16"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="33"/>
+      <c r="A35" s="34"/>
       <c r="B35" s="15" t="s">
         <v>14</v>
       </c>
@@ -5468,7 +5480,7 @@
       <c r="G35" s="16"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="33"/>
+      <c r="A36" s="34"/>
       <c r="B36" s="15" t="s">
         <v>76</v>
       </c>
@@ -5478,12 +5490,14 @@
         <v>30</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="G36" s="16"/>
+        <v>80</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="33"/>
+      <c r="A37" s="34"/>
       <c r="B37" s="15" t="s">
         <v>77</v>
       </c>
@@ -5498,7 +5512,7 @@
       <c r="G37" s="16"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="34"/>
+      <c r="A38" s="35"/>
       <c r="B38" s="15" t="s">
         <v>62</v>
       </c>
@@ -5513,12 +5527,20 @@
       <c r="G38" s="16"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="14"/>
-      <c r="B39" s="15"/>
+      <c r="A39" s="14">
+        <v>46084</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>60</v>
+      </c>
       <c r="C39" s="15"/>
       <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
+      <c r="E39" s="15">
+        <v>5</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="G39" s="16"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -5622,20 +5644,20 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
+  <autoFilter ref="A1:F38" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
   <mergeCells count="12">
+    <mergeCell ref="A33:A38"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A29:A31"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="A33:A38"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:F1000">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -5711,7 +5733,7 @@
       </c>
       <c r="D3" s="3">
         <f>SUM('Nhập xuất tồn'!D3)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E3" s="3">
         <f>SUM('Nhập xuất tồn'!E3)</f>
@@ -5719,14 +5741,14 @@
       </c>
       <c r="F3" s="3">
         <f>SUM(C3+D3-E3)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G3" s="4">
         <v>1</v>
       </c>
       <c r="H3" s="3">
         <f>SUM(F3-G3)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -5738,26 +5760,26 @@
       </c>
       <c r="C4" s="3">
         <f>SUM('Nhập xuất tồn'!C4)</f>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D4" s="3">
         <f>SUM('Nhập xuất tồn'!D4)</f>
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="E4" s="3">
         <f>SUM('Nhập xuất tồn'!E4)</f>
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="F4" s="3">
         <f>SUM(C4+D4-E4)</f>
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="G4" s="4">
         <v>14</v>
       </c>
       <c r="H4" s="3">
         <f>SUM(F4-G4)</f>
-        <v>175</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -6192,19 +6214,19 @@
       <c r="B19" s="36"/>
       <c r="C19" s="10">
         <f>SUM(C3:C17)</f>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D19" s="10">
         <f>SUM(D3:D17)</f>
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="E19" s="10">
         <f>SUM(E3:E17)</f>
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
@@ -6212,7 +6234,7 @@
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>190</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760CD15F-E414-4B45-99A5-AA1AD9AB9D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5544286-BE7C-4B84-AD47-3B8942A4CB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="83">
   <si>
     <t>VNSH01</t>
   </si>
@@ -245,9 +245,6 @@
     <t>Đã trả (24/02/26)</t>
   </si>
   <si>
-    <t>Chưa trả</t>
-  </si>
-  <si>
     <t>Đã trả (26/02/26)</t>
   </si>
   <si>
@@ -279,6 +276,15 @@
   </si>
   <si>
     <t>Đã trả (03/03/26)</t>
+  </si>
+  <si>
+    <t>Đã trả (04/03/26)</t>
+  </si>
+  <si>
+    <t>Hương</t>
+  </si>
+  <si>
+    <t>Đã trả 6 VNSH02</t>
   </si>
 </sst>
 </file>
@@ -1053,18 +1059,18 @@
       </c>
       <c r="E3" s="3">
         <f>Xuất!AH4+Huỷ!AH3</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3">
         <f>C3+D3-E3</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3" s="4">
         <v>1</v>
       </c>
       <c r="H3" s="3">
         <f>F3-G3</f>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1084,18 +1090,18 @@
       </c>
       <c r="E4" s="3">
         <f>Xuất!AH5+Huỷ!AH4</f>
-        <v>78</v>
+        <v>264</v>
       </c>
       <c r="F4" s="3">
         <f>C4+D4-E4</f>
-        <v>219</v>
+        <v>33</v>
       </c>
       <c r="G4" s="4">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" ref="H4:H22" si="0">F4-G4</f>
-        <v>203</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1653,7 +1659,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C23" s="3">
         <f>'[1]Nhập xuất tồn'!F23</f>
@@ -1692,19 +1698,19 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
-        <v>78</v>
+        <v>265</v>
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>243</v>
+        <v>56</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H24" s="3">
         <f>SUM(H3:H23)</f>
-        <v>225</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -2744,7 +2750,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -2993,7 +2999,9 @@
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="F4" s="5">
+        <v>1</v>
+      </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
@@ -3023,7 +3031,7 @@
       <c r="AG4" s="5"/>
       <c r="AH4" s="5">
         <f>SUM(C4:AG4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
@@ -3040,7 +3048,9 @@
       <c r="E5" s="5">
         <v>75</v>
       </c>
-      <c r="F5" s="5"/>
+      <c r="F5" s="5">
+        <v>186</v>
+      </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -3070,7 +3080,7 @@
       <c r="AG5" s="5"/>
       <c r="AH5" s="5">
         <f t="shared" ref="AH5:AH18" si="0">SUM(C5:AG5)</f>
-        <v>78</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
@@ -3837,7 +3847,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -5343,10 +5353,10 @@
         <v>100</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -5360,7 +5370,7 @@
         <v>30</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G28" s="16"/>
     </row>
@@ -5379,14 +5389,14 @@
         <v>5</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="34"/>
       <c r="B30" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C30" s="15"/>
       <c r="D30" s="15"/>
@@ -5394,7 +5404,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G30" s="16"/>
     </row>
@@ -5408,8 +5418,8 @@
       <c r="E31" s="15">
         <v>20</v>
       </c>
-      <c r="F31" s="18" t="s">
-        <v>69</v>
+      <c r="F31" s="15" t="s">
+        <v>80</v>
       </c>
       <c r="G31" s="16"/>
     </row>
@@ -5426,10 +5436,10 @@
         <v>30</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -5445,7 +5455,7 @@
         <v>10</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G33" s="16"/>
     </row>
@@ -5460,7 +5470,7 @@
         <v>10</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="G34" s="16"/>
     </row>
@@ -5475,14 +5485,14 @@
         <v>2</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G35" s="16"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="34"/>
       <c r="B36" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C36" s="15"/>
       <c r="D36" s="15"/>
@@ -5490,16 +5500,16 @@
         <v>30</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="34"/>
       <c r="B37" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C37" s="15"/>
       <c r="D37" s="15"/>
@@ -5507,7 +5517,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G37" s="16"/>
     </row>
@@ -5522,7 +5532,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="G38" s="16"/>
     </row>
@@ -5539,26 +5549,40 @@
         <v>5</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G39" s="16"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="14"/>
-      <c r="B40" s="15"/>
+      <c r="A40" s="33">
+        <v>46085</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>64</v>
+      </c>
       <c r="C40" s="15"/>
       <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
+      <c r="E40" s="15">
+        <v>30</v>
+      </c>
       <c r="F40" s="15"/>
-      <c r="G40" s="16"/>
+      <c r="G40" s="16" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="14"/>
-      <c r="B41" s="15"/>
+      <c r="A41" s="35"/>
+      <c r="B41" s="15" t="s">
+        <v>81</v>
+      </c>
       <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
+      <c r="D41" s="15">
+        <v>1</v>
+      </c>
       <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
+      <c r="F41" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="G41" s="16"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -5645,7 +5669,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F38" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="A40:A41"/>
     <mergeCell ref="A33:A38"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A24:A26"/>
@@ -5737,18 +5762,18 @@
       </c>
       <c r="E3" s="3">
         <f>SUM('Nhập xuất tồn'!E3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3">
         <f>SUM(C3+D3-E3)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3" s="4">
         <v>1</v>
       </c>
       <c r="H3" s="3">
         <f>SUM(F3-G3)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -5768,18 +5793,18 @@
       </c>
       <c r="E4" s="3">
         <f>SUM('Nhập xuất tồn'!E4)</f>
-        <v>78</v>
+        <v>264</v>
       </c>
       <c r="F4" s="3">
         <f>SUM(C4+D4-E4)</f>
-        <v>219</v>
+        <v>33</v>
       </c>
       <c r="G4" s="4">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H4" s="3">
         <f>SUM(F4-G4)</f>
-        <v>205</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -6180,7 +6205,7 @@
         <v>21</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18" s="3">
         <f>'Nhập xuất tồn'!C23</f>
@@ -6222,19 +6247,19 @@
       </c>
       <c r="E19" s="10">
         <f>SUM(E3:E17)</f>
-        <v>78</v>
+        <v>265</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>243</v>
+        <v>56</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>228</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5544286-BE7C-4B84-AD47-3B8942A4CB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10E6D8E2-B6DC-4AC8-8474-FE6DB27B3931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="D3" s="3">
         <f>Nhập!AH3</f>
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E3" s="3">
         <f>Xuất!AH4+Huỷ!AH3</f>
@@ -1063,14 +1063,14 @@
       </c>
       <c r="F3" s="3">
         <f>C3+D3-E3</f>
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="3">
         <f>F3-G3</f>
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1086,22 +1086,22 @@
       </c>
       <c r="D4" s="3">
         <f>Nhập!AH4</f>
-        <v>176</v>
+        <v>210</v>
       </c>
       <c r="E4" s="3">
         <f>Xuất!AH5+Huỷ!AH4</f>
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="F4" s="3">
         <f>C4+D4-E4</f>
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G4" s="4">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" ref="H4:H22" si="0">F4-G4</f>
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1694,23 +1694,23 @@
       </c>
       <c r="D24" s="3">
         <f t="shared" ref="D24:G24" si="2">SUM(D3:D22)</f>
-        <v>184</v>
+        <v>234</v>
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H24" s="3">
         <f>SUM(H3:H23)</f>
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1907,7 +1907,9 @@
         <v>8</v>
       </c>
       <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="G3" s="5">
+        <v>16</v>
+      </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -1936,7 +1938,7 @@
       <c r="AG3" s="5"/>
       <c r="AH3" s="5">
         <f>SUM(C3:AG3)</f>
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
@@ -1954,7 +1956,9 @@
         <v>104</v>
       </c>
       <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="G4" s="5">
+        <v>34</v>
+      </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
@@ -1983,7 +1987,7 @@
       <c r="AG4" s="5"/>
       <c r="AH4" s="5">
         <f t="shared" ref="AH4:AH19" si="0">SUM(C4:AG4)</f>
-        <v>176</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
@@ -3051,7 +3055,9 @@
       <c r="F5" s="5">
         <v>186</v>
       </c>
-      <c r="G5" s="5"/>
+      <c r="G5" s="5">
+        <v>24</v>
+      </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
@@ -3080,7 +3086,7 @@
       <c r="AG5" s="5"/>
       <c r="AH5" s="5">
         <f t="shared" ref="AH5:AH18" si="0">SUM(C5:AG5)</f>
-        <v>264</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
@@ -5758,7 +5764,7 @@
       </c>
       <c r="D3" s="3">
         <f>SUM('Nhập xuất tồn'!D3)</f>
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E3" s="3">
         <f>SUM('Nhập xuất tồn'!E3)</f>
@@ -5766,14 +5772,14 @@
       </c>
       <c r="F3" s="3">
         <f>SUM(C3+D3-E3)</f>
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G3" s="4">
         <v>1</v>
       </c>
       <c r="H3" s="3">
         <f>SUM(F3-G3)</f>
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -5789,22 +5795,22 @@
       </c>
       <c r="D4" s="3">
         <f>SUM('Nhập xuất tồn'!D4)</f>
-        <v>176</v>
+        <v>210</v>
       </c>
       <c r="E4" s="3">
         <f>SUM('Nhập xuất tồn'!E4)</f>
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="F4" s="3">
         <f>SUM(C4+D4-E4)</f>
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G4" s="4">
         <v>3</v>
       </c>
       <c r="H4" s="3">
         <f>SUM(F4-G4)</f>
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -6243,15 +6249,15 @@
       </c>
       <c r="D19" s="10">
         <f>SUM(D3:D17)</f>
-        <v>184</v>
+        <v>234</v>
       </c>
       <c r="E19" s="10">
         <f>SUM(E3:E17)</f>
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
@@ -6259,7 +6265,7 @@
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10E6D8E2-B6DC-4AC8-8474-FE6DB27B3931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8076D0-31DF-4D4F-AB45-B6B52853D206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="84">
   <si>
     <t>VNSH01</t>
   </si>
@@ -284,7 +284,10 @@
     <t>Hương</t>
   </si>
   <si>
-    <t>Đã trả 6 VNSH02</t>
+    <t>Chưa trả</t>
+  </si>
+  <si>
+    <t>Đã trả (05/03/26)</t>
   </si>
 </sst>
 </file>
@@ -549,16 +552,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1097,11 +1100,11 @@
         <v>43</v>
       </c>
       <c r="G4" s="4">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" ref="H4:H22" si="0">F4-G4</f>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1671,16 +1674,16 @@
       </c>
       <c r="E23" s="3">
         <f>SUM(Xuất!AH24)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F23" s="3">
         <f>SUM(C23+D23)-E23</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="3">
         <f>SUM(F23-G23)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1702,11 +1705,11 @@
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H24" s="3">
         <f>SUM(H3:H23)</f>
@@ -3860,7 +3863,9 @@
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
+      <c r="H24" s="5">
+        <v>3</v>
+      </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
@@ -3888,7 +3893,7 @@
       <c r="AG24" s="5"/>
       <c r="AH24" s="5">
         <f>SUM(C24:AG24)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4946,7 +4951,7 @@
       <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="32">
+      <c r="A2" s="35">
         <v>46055</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -4963,7 +4968,7 @@
       <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="32"/>
+      <c r="A3" s="35"/>
       <c r="B3" s="15" t="s">
         <v>40</v>
       </c>
@@ -4978,7 +4983,7 @@
       <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="32"/>
+      <c r="A4" s="35"/>
       <c r="B4" s="15" t="s">
         <v>41</v>
       </c>
@@ -4993,7 +4998,7 @@
       <c r="G4" s="16"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="32"/>
+      <c r="A5" s="35"/>
       <c r="B5" s="15" t="s">
         <v>42</v>
       </c>
@@ -5008,7 +5013,7 @@
       <c r="G5" s="16"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="32">
+      <c r="A6" s="35">
         <v>46056</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -5025,7 +5030,7 @@
       <c r="G6" s="16"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="32"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="15" t="s">
         <v>44</v>
       </c>
@@ -5040,7 +5045,7 @@
       <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="32">
+      <c r="A8" s="35">
         <v>46057</v>
       </c>
       <c r="B8" s="14" t="s">
@@ -5057,7 +5062,7 @@
       <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="32"/>
+      <c r="A9" s="35"/>
       <c r="B9" s="15" t="s">
         <v>40</v>
       </c>
@@ -5072,7 +5077,7 @@
       <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
+      <c r="A10" s="35">
         <v>46058</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -5089,7 +5094,7 @@
       <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="32"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="15" t="s">
         <v>50</v>
       </c>
@@ -5104,7 +5109,7 @@
       <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="32">
+      <c r="A12" s="35">
         <v>46059</v>
       </c>
       <c r="B12" s="15" t="s">
@@ -5121,7 +5126,7 @@
       <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="32"/>
+      <c r="A13" s="35"/>
       <c r="B13" s="15" t="s">
         <v>51</v>
       </c>
@@ -5153,7 +5158,7 @@
       <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="32">
+      <c r="A15" s="35">
         <v>46062</v>
       </c>
       <c r="B15" s="15" t="s">
@@ -5170,7 +5175,7 @@
       <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="32"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="15" t="s">
         <v>42</v>
       </c>
@@ -5219,7 +5224,7 @@
       <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="32">
+      <c r="A19" s="35">
         <v>46065</v>
       </c>
       <c r="B19" s="15" t="s">
@@ -5236,7 +5241,7 @@
       <c r="G19" s="16"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="32"/>
+      <c r="A20" s="35"/>
       <c r="B20" s="15" t="s">
         <v>50</v>
       </c>
@@ -5251,7 +5256,7 @@
       <c r="G20" s="16"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="33">
+      <c r="A21" s="32">
         <v>46076</v>
       </c>
       <c r="B21" s="15" t="s">
@@ -5283,7 +5288,7 @@
       <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="35"/>
+      <c r="A23" s="33"/>
       <c r="B23" s="15" t="s">
         <v>67</v>
       </c>
@@ -5298,7 +5303,7 @@
       <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="33">
+      <c r="A24" s="32">
         <v>46077</v>
       </c>
       <c r="B24" s="15" t="s">
@@ -5330,7 +5335,7 @@
       <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="35"/>
+      <c r="A26" s="33"/>
       <c r="B26" s="15" t="s">
         <v>14</v>
       </c>
@@ -5345,7 +5350,7 @@
       <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="33">
+      <c r="A27" s="32">
         <v>46078</v>
       </c>
       <c r="B27" s="15" t="s">
@@ -5366,7 +5371,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="35"/>
+      <c r="A28" s="33"/>
       <c r="B28" s="15" t="s">
         <v>50</v>
       </c>
@@ -5381,7 +5386,7 @@
       <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="33">
+      <c r="A29" s="32">
         <v>46079</v>
       </c>
       <c r="B29" s="15" t="s">
@@ -5415,7 +5420,7 @@
       <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="35"/>
+      <c r="A31" s="33"/>
       <c r="B31" s="15" t="s">
         <v>50</v>
       </c>
@@ -5449,7 +5454,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="33">
+      <c r="A33" s="32">
         <v>46083</v>
       </c>
       <c r="B33" s="15" t="s">
@@ -5528,7 +5533,7 @@
       <c r="G37" s="16"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="35"/>
+      <c r="A38" s="33"/>
       <c r="B38" s="15" t="s">
         <v>62</v>
       </c>
@@ -5560,7 +5565,7 @@
       <c r="G39" s="16"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="33">
+      <c r="A40" s="32">
         <v>46085</v>
       </c>
       <c r="B40" s="15" t="s">
@@ -5571,13 +5576,13 @@
       <c r="E40" s="15">
         <v>30</v>
       </c>
-      <c r="F40" s="15"/>
-      <c r="G40" s="16" t="s">
-        <v>82</v>
-      </c>
+      <c r="F40" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="G40" s="16"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="35"/>
+      <c r="A41" s="33"/>
       <c r="B41" s="15" t="s">
         <v>81</v>
       </c>
@@ -5592,12 +5597,20 @@
       <c r="G41" s="16"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="14"/>
-      <c r="B42" s="15"/>
+      <c r="A42" s="14">
+        <v>46086</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>62</v>
+      </c>
       <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
+      <c r="D42" s="15">
+        <v>20</v>
+      </c>
       <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
+      <c r="F42" s="15" t="s">
+        <v>82</v>
+      </c>
       <c r="G42" s="16"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -5676,11 +5689,6 @@
   </sheetData>
   <autoFilter ref="A1:F38" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
   <mergeCells count="13">
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A33:A38"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A21:A23"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="A15:A16"/>
@@ -5689,6 +5697,11 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A33:A38"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A21:A23"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:F1000">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -6223,11 +6236,11 @@
       </c>
       <c r="E18" s="3">
         <f>'Nhập xuất tồn'!E23</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F18" s="3">
         <f>'Nhập xuất tồn'!F23</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G18" s="4">
         <f>'Nhập xuất tồn'!G23</f>
@@ -6235,7 +6248,7 @@
       </c>
       <c r="H18" s="3">
         <f>'Nhập xuất tồn'!H23</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -6257,7 +6270,7 @@
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
@@ -6265,7 +6278,7 @@
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8076D0-31DF-4D4F-AB45-B6B52853D206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FB1DA5-9798-4243-88C7-CA90B7C6DA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
@@ -552,16 +552,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1062,18 +1062,18 @@
       </c>
       <c r="E3" s="3">
         <f>Xuất!AH4+Huỷ!AH3</f>
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F3" s="3">
         <f>C3+D3-E3</f>
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G3" s="4">
         <v>2</v>
       </c>
       <c r="H3" s="3">
         <f>F3-G3</f>
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1701,11 +1701,11 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="H24" s="3">
         <f>SUM(H3:H23)</f>
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -3011,7 +3011,9 @@
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
+      <c r="I4" s="5">
+        <v>20</v>
+      </c>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
@@ -3038,7 +3040,7 @@
       <c r="AG4" s="5"/>
       <c r="AH4" s="5">
         <f>SUM(C4:AG4)</f>
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
@@ -4951,7 +4953,7 @@
       <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="35">
+      <c r="A2" s="32">
         <v>46055</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -4968,7 +4970,7 @@
       <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="35"/>
+      <c r="A3" s="32"/>
       <c r="B3" s="15" t="s">
         <v>40</v>
       </c>
@@ -4983,7 +4985,7 @@
       <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
+      <c r="A4" s="32"/>
       <c r="B4" s="15" t="s">
         <v>41</v>
       </c>
@@ -4998,7 +5000,7 @@
       <c r="G4" s="16"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="35"/>
+      <c r="A5" s="32"/>
       <c r="B5" s="15" t="s">
         <v>42</v>
       </c>
@@ -5013,7 +5015,7 @@
       <c r="G5" s="16"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="35">
+      <c r="A6" s="32">
         <v>46056</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -5030,7 +5032,7 @@
       <c r="G6" s="16"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="35"/>
+      <c r="A7" s="32"/>
       <c r="B7" s="15" t="s">
         <v>44</v>
       </c>
@@ -5045,7 +5047,7 @@
       <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="35">
+      <c r="A8" s="32">
         <v>46057</v>
       </c>
       <c r="B8" s="14" t="s">
@@ -5062,7 +5064,7 @@
       <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="35"/>
+      <c r="A9" s="32"/>
       <c r="B9" s="15" t="s">
         <v>40</v>
       </c>
@@ -5077,7 +5079,7 @@
       <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="35">
+      <c r="A10" s="32">
         <v>46058</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -5094,7 +5096,7 @@
       <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="35"/>
+      <c r="A11" s="32"/>
       <c r="B11" s="15" t="s">
         <v>50</v>
       </c>
@@ -5109,7 +5111,7 @@
       <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="35">
+      <c r="A12" s="32">
         <v>46059</v>
       </c>
       <c r="B12" s="15" t="s">
@@ -5126,7 +5128,7 @@
       <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
+      <c r="A13" s="32"/>
       <c r="B13" s="15" t="s">
         <v>51</v>
       </c>
@@ -5158,7 +5160,7 @@
       <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="35">
+      <c r="A15" s="32">
         <v>46062</v>
       </c>
       <c r="B15" s="15" t="s">
@@ -5175,7 +5177,7 @@
       <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="35"/>
+      <c r="A16" s="32"/>
       <c r="B16" s="15" t="s">
         <v>42</v>
       </c>
@@ -5224,7 +5226,7 @@
       <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="35">
+      <c r="A19" s="32">
         <v>46065</v>
       </c>
       <c r="B19" s="15" t="s">
@@ -5241,7 +5243,7 @@
       <c r="G19" s="16"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="35"/>
+      <c r="A20" s="32"/>
       <c r="B20" s="15" t="s">
         <v>50</v>
       </c>
@@ -5256,7 +5258,7 @@
       <c r="G20" s="16"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="32">
+      <c r="A21" s="33">
         <v>46076</v>
       </c>
       <c r="B21" s="15" t="s">
@@ -5288,7 +5290,7 @@
       <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="33"/>
+      <c r="A23" s="35"/>
       <c r="B23" s="15" t="s">
         <v>67</v>
       </c>
@@ -5303,7 +5305,7 @@
       <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="32">
+      <c r="A24" s="33">
         <v>46077</v>
       </c>
       <c r="B24" s="15" t="s">
@@ -5335,7 +5337,7 @@
       <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="33"/>
+      <c r="A26" s="35"/>
       <c r="B26" s="15" t="s">
         <v>14</v>
       </c>
@@ -5350,7 +5352,7 @@
       <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="32">
+      <c r="A27" s="33">
         <v>46078</v>
       </c>
       <c r="B27" s="15" t="s">
@@ -5371,7 +5373,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="33"/>
+      <c r="A28" s="35"/>
       <c r="B28" s="15" t="s">
         <v>50</v>
       </c>
@@ -5386,7 +5388,7 @@
       <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="32">
+      <c r="A29" s="33">
         <v>46079</v>
       </c>
       <c r="B29" s="15" t="s">
@@ -5420,7 +5422,7 @@
       <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="33"/>
+      <c r="A31" s="35"/>
       <c r="B31" s="15" t="s">
         <v>50</v>
       </c>
@@ -5454,7 +5456,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="32">
+      <c r="A33" s="33">
         <v>46083</v>
       </c>
       <c r="B33" s="15" t="s">
@@ -5533,7 +5535,7 @@
       <c r="G37" s="16"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="33"/>
+      <c r="A38" s="35"/>
       <c r="B38" s="15" t="s">
         <v>62</v>
       </c>
@@ -5565,7 +5567,7 @@
       <c r="G39" s="16"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="32">
+      <c r="A40" s="33">
         <v>46085</v>
       </c>
       <c r="B40" s="15" t="s">
@@ -5582,7 +5584,7 @@
       <c r="G40" s="16"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="33"/>
+      <c r="A41" s="35"/>
       <c r="B41" s="15" t="s">
         <v>81</v>
       </c>
@@ -5689,6 +5691,11 @@
   </sheetData>
   <autoFilter ref="A1:F38" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
   <mergeCells count="13">
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A33:A38"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A21:A23"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="A15:A16"/>
@@ -5697,11 +5704,6 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A33:A38"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A21:A23"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:F1000">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -5781,18 +5783,18 @@
       </c>
       <c r="E3" s="3">
         <f>SUM('Nhập xuất tồn'!E3)</f>
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F3" s="3">
         <f>SUM(C3+D3-E3)</f>
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G3" s="4">
         <v>1</v>
       </c>
       <c r="H3" s="3">
         <f>SUM(F3-G3)</f>
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -6266,11 +6268,11 @@
       </c>
       <c r="E19" s="10">
         <f>SUM(E3:E17)</f>
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
@@ -6278,7 +6280,7 @@
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FB1DA5-9798-4243-88C7-CA90B7C6DA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA37613-04AE-4A51-90C0-13645666BA6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="87">
   <si>
     <t>VNSH01</t>
   </si>
@@ -284,10 +284,19 @@
     <t>Hương</t>
   </si>
   <si>
-    <t>Chưa trả</t>
-  </si>
-  <si>
     <t>Đã trả (05/03/26)</t>
+  </si>
+  <si>
+    <t>Đã trả (07/03/26)</t>
+  </si>
+  <si>
+    <t>Skytech</t>
+  </si>
+  <si>
+    <t>Hay Huế</t>
+  </si>
+  <si>
+    <t>Đã trả (09/03/26)</t>
   </si>
 </sst>
 </file>
@@ -1093,18 +1102,18 @@
       </c>
       <c r="E4" s="3">
         <f>Xuất!AH5+Huỷ!AH4</f>
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F4" s="3">
         <f>C4+D4-E4</f>
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G4" s="4">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" ref="H4:H22" si="0">F4-G4</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1701,19 +1710,19 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H24" s="3">
         <f>SUM(H3:H23)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -3066,7 +3075,9 @@
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
+      <c r="K5" s="5">
+        <v>2</v>
+      </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
@@ -3091,7 +3102,7 @@
       <c r="AG5" s="5"/>
       <c r="AH5" s="5">
         <f t="shared" ref="AH5:AH18" si="0">SUM(C5:AG5)</f>
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
@@ -5579,7 +5590,7 @@
         <v>30</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G40" s="16"/>
     </row>
@@ -5611,26 +5622,40 @@
       </c>
       <c r="E42" s="15"/>
       <c r="F42" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G42" s="16"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="15"/>
-      <c r="B43" s="15"/>
+      <c r="A43" s="33">
+        <v>46090</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>84</v>
+      </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
+      <c r="E43" s="15">
+        <v>1</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>86</v>
+      </c>
       <c r="G43" s="16"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="15"/>
-      <c r="B44" s="15"/>
+      <c r="A44" s="35"/>
+      <c r="B44" s="15" t="s">
+        <v>85</v>
+      </c>
       <c r="C44" s="15"/>
       <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
+      <c r="E44" s="15">
+        <v>1</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>86</v>
+      </c>
       <c r="G44" s="16"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -5690,7 +5715,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F38" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
-  <mergeCells count="13">
+  <mergeCells count="14">
+    <mergeCell ref="A43:A44"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="A33:A38"/>
     <mergeCell ref="A27:A28"/>
@@ -5790,11 +5816,12 @@
         <v>5</v>
       </c>
       <c r="G3" s="4">
-        <v>1</v>
+        <f>'Nhập xuất tồn'!G3</f>
+        <v>2</v>
       </c>
       <c r="H3" s="3">
         <f>SUM(F3-G3)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -5814,18 +5841,19 @@
       </c>
       <c r="E4" s="3">
         <f>SUM('Nhập xuất tồn'!E4)</f>
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F4" s="3">
         <f>SUM(C4+D4-E4)</f>
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G4" s="4">
-        <v>3</v>
+        <f>'Nhập xuất tồn'!G4</f>
+        <v>32</v>
       </c>
       <c r="H4" s="3">
         <f>SUM(F4-G4)</f>
-        <v>40</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -6268,19 +6296,19 @@
       </c>
       <c r="E19" s="10">
         <f>SUM(E3:E17)</f>
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA37613-04AE-4A51-90C0-13645666BA6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A09380-78DD-4B1D-8418-0FA9AF3CE24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
@@ -561,16 +561,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4964,7 +4964,7 @@
       <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="32">
+      <c r="A2" s="35">
         <v>46055</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -4981,7 +4981,7 @@
       <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="32"/>
+      <c r="A3" s="35"/>
       <c r="B3" s="15" t="s">
         <v>40</v>
       </c>
@@ -4996,7 +4996,7 @@
       <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="32"/>
+      <c r="A4" s="35"/>
       <c r="B4" s="15" t="s">
         <v>41</v>
       </c>
@@ -5011,7 +5011,7 @@
       <c r="G4" s="16"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="32"/>
+      <c r="A5" s="35"/>
       <c r="B5" s="15" t="s">
         <v>42</v>
       </c>
@@ -5026,7 +5026,7 @@
       <c r="G5" s="16"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="32">
+      <c r="A6" s="35">
         <v>46056</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -5043,7 +5043,7 @@
       <c r="G6" s="16"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="32"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="15" t="s">
         <v>44</v>
       </c>
@@ -5058,7 +5058,7 @@
       <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="32">
+      <c r="A8" s="35">
         <v>46057</v>
       </c>
       <c r="B8" s="14" t="s">
@@ -5075,7 +5075,7 @@
       <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="32"/>
+      <c r="A9" s="35"/>
       <c r="B9" s="15" t="s">
         <v>40</v>
       </c>
@@ -5090,7 +5090,7 @@
       <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
+      <c r="A10" s="35">
         <v>46058</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -5107,7 +5107,7 @@
       <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="32"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="15" t="s">
         <v>50</v>
       </c>
@@ -5122,7 +5122,7 @@
       <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="32">
+      <c r="A12" s="35">
         <v>46059</v>
       </c>
       <c r="B12" s="15" t="s">
@@ -5139,7 +5139,7 @@
       <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="32"/>
+      <c r="A13" s="35"/>
       <c r="B13" s="15" t="s">
         <v>51</v>
       </c>
@@ -5171,7 +5171,7 @@
       <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="32">
+      <c r="A15" s="35">
         <v>46062</v>
       </c>
       <c r="B15" s="15" t="s">
@@ -5188,7 +5188,7 @@
       <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="32"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="15" t="s">
         <v>42</v>
       </c>
@@ -5237,7 +5237,7 @@
       <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="32">
+      <c r="A19" s="35">
         <v>46065</v>
       </c>
       <c r="B19" s="15" t="s">
@@ -5254,7 +5254,7 @@
       <c r="G19" s="16"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="32"/>
+      <c r="A20" s="35"/>
       <c r="B20" s="15" t="s">
         <v>50</v>
       </c>
@@ -5269,7 +5269,7 @@
       <c r="G20" s="16"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="33">
+      <c r="A21" s="32">
         <v>46076</v>
       </c>
       <c r="B21" s="15" t="s">
@@ -5301,7 +5301,7 @@
       <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="35"/>
+      <c r="A23" s="33"/>
       <c r="B23" s="15" t="s">
         <v>67</v>
       </c>
@@ -5316,7 +5316,7 @@
       <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="33">
+      <c r="A24" s="32">
         <v>46077</v>
       </c>
       <c r="B24" s="15" t="s">
@@ -5348,7 +5348,7 @@
       <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="35"/>
+      <c r="A26" s="33"/>
       <c r="B26" s="15" t="s">
         <v>14</v>
       </c>
@@ -5363,7 +5363,7 @@
       <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="33">
+      <c r="A27" s="32">
         <v>46078</v>
       </c>
       <c r="B27" s="15" t="s">
@@ -5384,7 +5384,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="35"/>
+      <c r="A28" s="33"/>
       <c r="B28" s="15" t="s">
         <v>50</v>
       </c>
@@ -5399,7 +5399,7 @@
       <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="33">
+      <c r="A29" s="32">
         <v>46079</v>
       </c>
       <c r="B29" s="15" t="s">
@@ -5433,7 +5433,7 @@
       <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="35"/>
+      <c r="A31" s="33"/>
       <c r="B31" s="15" t="s">
         <v>50</v>
       </c>
@@ -5467,7 +5467,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="33">
+      <c r="A33" s="32">
         <v>46083</v>
       </c>
       <c r="B33" s="15" t="s">
@@ -5546,7 +5546,7 @@
       <c r="G37" s="16"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="35"/>
+      <c r="A38" s="33"/>
       <c r="B38" s="15" t="s">
         <v>62</v>
       </c>
@@ -5578,7 +5578,7 @@
       <c r="G39" s="16"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="33">
+      <c r="A40" s="32">
         <v>46085</v>
       </c>
       <c r="B40" s="15" t="s">
@@ -5595,7 +5595,7 @@
       <c r="G40" s="16"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="35"/>
+      <c r="A41" s="33"/>
       <c r="B41" s="15" t="s">
         <v>81</v>
       </c>
@@ -5627,7 +5627,7 @@
       <c r="G42" s="16"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="33">
+      <c r="A43" s="32">
         <v>46090</v>
       </c>
       <c r="B43" s="15" t="s">
@@ -5644,7 +5644,7 @@
       <c r="G43" s="16"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="35"/>
+      <c r="A44" s="33"/>
       <c r="B44" s="15" t="s">
         <v>85</v>
       </c>
@@ -5716,11 +5716,6 @@
   </sheetData>
   <autoFilter ref="A1:F38" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
   <mergeCells count="14">
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A33:A38"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A24:A26"/>
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A29:A31"/>
@@ -5730,6 +5725,11 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A33:A38"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A24:A26"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:F1000">
     <cfRule type="expression" dxfId="1" priority="1">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A09380-78DD-4B1D-8418-0FA9AF3CE24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CBAE52-3B6E-4B16-9448-FC627EE2091D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="89">
   <si>
     <t>VNSH01</t>
   </si>
@@ -297,6 +297,12 @@
   </si>
   <si>
     <t>Đã trả (09/03/26)</t>
+  </si>
+  <si>
+    <t>ĐL Anh Sửu</t>
+  </si>
+  <si>
+    <t>Đã trả (11/03/26)</t>
   </si>
 </sst>
 </file>
@@ -564,10 +570,10 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1102,19 +1108,14 @@
       </c>
       <c r="E4" s="3">
         <f>Xuất!AH5+Huỷ!AH4</f>
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="F4" s="3">
         <f>C4+D4-E4</f>
-        <v>41</v>
-      </c>
-      <c r="G4" s="4">
-        <v>32</v>
-      </c>
-      <c r="H4" s="3">
-        <f t="shared" ref="H4:H22" si="0">F4-G4</f>
-        <v>9</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -1136,14 +1137,14 @@
         <v>0</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" ref="F5:F22" si="1">C5+D5-E5</f>
+        <f t="shared" ref="F5:F22" si="0">C5+D5-E5</f>
         <v>0</v>
       </c>
       <c r="G5" s="4">
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H5:H22" si="1">F5-G5</f>
         <v>0</v>
       </c>
     </row>
@@ -1167,14 +1168,14 @@
         <v>0</v>
       </c>
       <c r="F6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1198,14 +1199,14 @@
         <v>0</v>
       </c>
       <c r="F7" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1229,14 +1230,14 @@
         <v>0</v>
       </c>
       <c r="F8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1260,14 +1261,14 @@
         <v>0</v>
       </c>
       <c r="F9" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1291,14 +1292,14 @@
         <v>0</v>
       </c>
       <c r="F10" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="G10" s="4">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1322,14 +1323,14 @@
         <v>0</v>
       </c>
       <c r="F11" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1353,14 +1354,14 @@
         <v>0</v>
       </c>
       <c r="F12" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1384,14 +1385,14 @@
         <v>0</v>
       </c>
       <c r="F13" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1415,14 +1416,14 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="4">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1446,14 +1447,14 @@
         <v>0</v>
       </c>
       <c r="F15" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1477,12 +1478,12 @@
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1506,12 +1507,12 @@
         <v>0</v>
       </c>
       <c r="F17" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1535,12 +1536,12 @@
         <v>0</v>
       </c>
       <c r="F18" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1564,12 +1565,12 @@
         <v>0</v>
       </c>
       <c r="F19" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1593,14 +1594,14 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G20" s="4">
         <v>1</v>
       </c>
       <c r="H20" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1624,14 +1625,14 @@
         <v>0</v>
       </c>
       <c r="F21" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="4">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1655,14 +1656,14 @@
         <v>0</v>
       </c>
       <c r="F22" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="G22" s="4">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -1710,19 +1711,19 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="H24" s="3">
         <f>SUM(H3:H23)</f>
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -3079,7 +3080,9 @@
         <v>2</v>
       </c>
       <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="M5" s="5">
+        <v>16</v>
+      </c>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
@@ -3102,7 +3105,7 @@
       <c r="AG5" s="5"/>
       <c r="AH5" s="5">
         <f t="shared" ref="AH5:AH18" si="0">SUM(C5:AG5)</f>
-        <v>290</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
@@ -5286,7 +5289,7 @@
       <c r="G21" s="16"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
+      <c r="A22" s="33"/>
       <c r="B22" s="15" t="s">
         <v>65</v>
       </c>
@@ -5301,7 +5304,7 @@
       <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="33"/>
+      <c r="A23" s="34"/>
       <c r="B23" s="15" t="s">
         <v>67</v>
       </c>
@@ -5333,7 +5336,7 @@
       <c r="G24" s="16"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="34"/>
+      <c r="A25" s="33"/>
       <c r="B25" s="15" t="s">
         <v>64</v>
       </c>
@@ -5348,7 +5351,7 @@
       <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="33"/>
+      <c r="A26" s="34"/>
       <c r="B26" s="15" t="s">
         <v>14</v>
       </c>
@@ -5384,7 +5387,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="33"/>
+      <c r="A28" s="34"/>
       <c r="B28" s="15" t="s">
         <v>50</v>
       </c>
@@ -5418,7 +5421,7 @@
       <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="34"/>
+      <c r="A30" s="33"/>
       <c r="B30" s="15" t="s">
         <v>70</v>
       </c>
@@ -5433,7 +5436,7 @@
       <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="33"/>
+      <c r="A31" s="34"/>
       <c r="B31" s="15" t="s">
         <v>50</v>
       </c>
@@ -5484,7 +5487,7 @@
       <c r="G33" s="16"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="34"/>
+      <c r="A34" s="33"/>
       <c r="B34" s="15" t="s">
         <v>50</v>
       </c>
@@ -5499,7 +5502,7 @@
       <c r="G34" s="16"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="34"/>
+      <c r="A35" s="33"/>
       <c r="B35" s="15" t="s">
         <v>14</v>
       </c>
@@ -5514,7 +5517,7 @@
       <c r="G35" s="16"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="34"/>
+      <c r="A36" s="33"/>
       <c r="B36" s="15" t="s">
         <v>75</v>
       </c>
@@ -5531,7 +5534,7 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="34"/>
+      <c r="A37" s="33"/>
       <c r="B37" s="15" t="s">
         <v>76</v>
       </c>
@@ -5546,7 +5549,7 @@
       <c r="G37" s="16"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="33"/>
+      <c r="A38" s="34"/>
       <c r="B38" s="15" t="s">
         <v>62</v>
       </c>
@@ -5595,7 +5598,7 @@
       <c r="G40" s="16"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="33"/>
+      <c r="A41" s="34"/>
       <c r="B41" s="15" t="s">
         <v>81</v>
       </c>
@@ -5644,7 +5647,7 @@
       <c r="G43" s="16"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="33"/>
+      <c r="A44" s="34"/>
       <c r="B44" s="15" t="s">
         <v>85</v>
       </c>
@@ -5659,21 +5662,37 @@
       <c r="G44" s="16"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="15"/>
-      <c r="B45" s="15"/>
+      <c r="A45" s="14">
+        <v>46091</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>87</v>
+      </c>
       <c r="C45" s="15"/>
       <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
+      <c r="E45" s="15">
+        <v>10</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>88</v>
+      </c>
       <c r="G45" s="16"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="15"/>
-      <c r="B46" s="15"/>
+      <c r="A46" s="14">
+        <v>46092</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>50</v>
+      </c>
       <c r="C46" s="15"/>
       <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
+      <c r="E46" s="15">
+        <v>6</v>
+      </c>
+      <c r="F46" s="15" t="s">
+        <v>88</v>
+      </c>
       <c r="G46" s="16"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -5716,6 +5735,11 @@
   </sheetData>
   <autoFilter ref="A1:F38" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
   <mergeCells count="14">
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A33:A38"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A24:A26"/>
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A29:A31"/>
@@ -5725,11 +5749,6 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A33:A38"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A24:A26"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:F1000">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -5841,19 +5860,19 @@
       </c>
       <c r="E4" s="3">
         <f>SUM('Nhập xuất tồn'!E4)</f>
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="F4" s="3">
         <f>SUM(C4+D4-E4)</f>
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="G4" s="4">
         <f>'Nhập xuất tồn'!G4</f>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H4" s="3">
         <f>SUM(F4-G4)</f>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -6296,19 +6315,19 @@
       </c>
       <c r="E19" s="10">
         <f>SUM(E3:E17)</f>
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CBAE52-3B6E-4B16-9448-FC627EE2091D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5F5EB6-8D1E-4E6F-8DE2-2D71E33DB29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
-    <sheet name="Nhập" sheetId="2" r:id="rId2"/>
-    <sheet name="Xuất" sheetId="3" r:id="rId3"/>
-    <sheet name="Huỷ" sheetId="4" r:id="rId4"/>
-    <sheet name="Ghi chú" sheetId="5" r:id="rId5"/>
+    <sheet name="Xuất" sheetId="3" r:id="rId2"/>
+    <sheet name="Nhập" sheetId="2" r:id="rId3"/>
+    <sheet name="Ghi chú" sheetId="5" r:id="rId4"/>
+    <sheet name="Huỷ" sheetId="4" r:id="rId5"/>
     <sheet name="Chốt kho" sheetId="6" r:id="rId6"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ghi chú'!$A$1:$F$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ghi chú'!$A$1:$F$38</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="90">
   <si>
     <t>VNSH01</t>
   </si>
@@ -152,9 +152,6 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>Danh Sách Thiết Bị Gửi Trên Bảo Hành - Sản Xuất Tháng 02</t>
-  </si>
-  <si>
     <t>Đã trả (02/02/26)</t>
   </si>
   <si>
@@ -303,6 +300,12 @@
   </si>
   <si>
     <t>Đã trả (11/03/26)</t>
+  </si>
+  <si>
+    <t>Danh Sách Thiết Bị Gửi Trên Bảo Hành - Sản Xuất Tháng 03</t>
+  </si>
+  <si>
+    <t>Chưa trả</t>
   </si>
 </sst>
 </file>
@@ -472,7 +475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -519,9 +522,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -537,9 +537,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -552,6 +549,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -559,12 +562,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1023,40 +1020,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="25"/>
+      <c r="A1" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="18" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1073,22 +1070,22 @@
       </c>
       <c r="D3" s="3">
         <f>Nhập!AH3</f>
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E3" s="3">
         <f>Xuất!AH4+Huỷ!AH3</f>
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F3" s="3">
         <f>C3+D3-E3</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G3" s="4">
         <v>2</v>
       </c>
       <c r="H3" s="3">
         <f>F3-G3</f>
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1672,7 +1669,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C23" s="3">
         <f>'[1]Nhập xuất tồn'!F23</f>
@@ -1697,25 +1694,25 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="26"/>
+      <c r="B24" s="24"/>
       <c r="C24" s="3">
         <f>SUM(C3:C22)</f>
         <v>134</v>
       </c>
       <c r="D24" s="3">
         <f t="shared" ref="D24:G24" si="2">SUM(D3:D22)</f>
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
@@ -1723,7 +1720,7 @@
       </c>
       <c r="H24" s="3">
         <f>SUM(H3:H23)</f>
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1755,6 +1752,1115 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:AH24"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.5703125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" style="8" customWidth="1"/>
+    <col min="3" max="34" width="5.28515625" style="8" customWidth="1"/>
+    <col min="35" max="16384" width="8.85546875" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A1" s="25"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
+      <c r="AB1" s="25"/>
+      <c r="AC1" s="25"/>
+      <c r="AD1" s="25"/>
+      <c r="AE1" s="25"/>
+      <c r="AF1" s="25"/>
+      <c r="AG1" s="25"/>
+      <c r="AH1" s="25"/>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="26"/>
+      <c r="AB2" s="26"/>
+      <c r="AC2" s="26"/>
+      <c r="AD2" s="26"/>
+      <c r="AE2" s="26"/>
+      <c r="AF2" s="26"/>
+      <c r="AG2" s="26"/>
+      <c r="AH2" s="26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2</v>
+      </c>
+      <c r="E3" s="5">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5">
+        <v>4</v>
+      </c>
+      <c r="G3" s="5">
+        <v>5</v>
+      </c>
+      <c r="H3" s="5">
+        <v>6</v>
+      </c>
+      <c r="I3" s="5">
+        <v>7</v>
+      </c>
+      <c r="J3" s="5">
+        <v>8</v>
+      </c>
+      <c r="K3" s="5">
+        <v>9</v>
+      </c>
+      <c r="L3" s="5">
+        <v>10</v>
+      </c>
+      <c r="M3" s="5">
+        <v>11</v>
+      </c>
+      <c r="N3" s="5">
+        <v>12</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="5">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>15</v>
+      </c>
+      <c r="R3" s="5">
+        <v>16</v>
+      </c>
+      <c r="S3" s="5">
+        <v>17</v>
+      </c>
+      <c r="T3" s="5">
+        <v>18</v>
+      </c>
+      <c r="U3" s="5">
+        <v>19</v>
+      </c>
+      <c r="V3" s="5">
+        <v>20</v>
+      </c>
+      <c r="W3" s="5">
+        <v>21</v>
+      </c>
+      <c r="X3" s="5">
+        <v>22</v>
+      </c>
+      <c r="Y3" s="5">
+        <v>23</v>
+      </c>
+      <c r="Z3" s="5">
+        <v>24</v>
+      </c>
+      <c r="AA3" s="5">
+        <v>25</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>26</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>27</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>28</v>
+      </c>
+      <c r="AE3" s="5">
+        <v>29</v>
+      </c>
+      <c r="AF3" s="5">
+        <v>30</v>
+      </c>
+      <c r="AG3" s="5">
+        <v>31</v>
+      </c>
+      <c r="AH3" s="26"/>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5">
+        <v>20</v>
+      </c>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5"/>
+      <c r="AG4" s="5"/>
+      <c r="AH4" s="5">
+        <f>SUM(C4:AG4)</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>2</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5">
+        <v>3</v>
+      </c>
+      <c r="E5" s="5">
+        <v>75</v>
+      </c>
+      <c r="F5" s="5">
+        <v>186</v>
+      </c>
+      <c r="G5" s="5">
+        <v>24</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5">
+        <v>2</v>
+      </c>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5">
+        <v>16</v>
+      </c>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
+      <c r="Z5" s="5"/>
+      <c r="AA5" s="5"/>
+      <c r="AB5" s="5"/>
+      <c r="AC5" s="5"/>
+      <c r="AD5" s="5"/>
+      <c r="AE5" s="5"/>
+      <c r="AF5" s="5"/>
+      <c r="AG5" s="5"/>
+      <c r="AH5" s="5">
+        <f t="shared" ref="AH5:AH18" si="0">SUM(C5:AG5)</f>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>3</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5"/>
+      <c r="AA6" s="5"/>
+      <c r="AB6" s="5"/>
+      <c r="AC6" s="5"/>
+      <c r="AD6" s="5"/>
+      <c r="AE6" s="5"/>
+      <c r="AF6" s="5"/>
+      <c r="AG6" s="5"/>
+      <c r="AH6" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="5"/>
+      <c r="AA7" s="5"/>
+      <c r="AB7" s="5"/>
+      <c r="AC7" s="5"/>
+      <c r="AD7" s="5"/>
+      <c r="AE7" s="5"/>
+      <c r="AF7" s="5"/>
+      <c r="AG7" s="5"/>
+      <c r="AH7" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>5</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="5"/>
+      <c r="AA8" s="5"/>
+      <c r="AB8" s="5"/>
+      <c r="AC8" s="5"/>
+      <c r="AD8" s="5"/>
+      <c r="AE8" s="5"/>
+      <c r="AF8" s="5"/>
+      <c r="AG8" s="5"/>
+      <c r="AH8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>6</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
+      <c r="Z9" s="5"/>
+      <c r="AA9" s="5"/>
+      <c r="AB9" s="5"/>
+      <c r="AC9" s="5"/>
+      <c r="AD9" s="5"/>
+      <c r="AE9" s="5"/>
+      <c r="AF9" s="5"/>
+      <c r="AG9" s="5"/>
+      <c r="AH9" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>7</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="5"/>
+      <c r="AA10" s="5"/>
+      <c r="AB10" s="5"/>
+      <c r="AC10" s="5"/>
+      <c r="AD10" s="5"/>
+      <c r="AE10" s="5"/>
+      <c r="AF10" s="5"/>
+      <c r="AG10" s="5"/>
+      <c r="AH10" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>8</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="5"/>
+      <c r="AA11" s="5"/>
+      <c r="AB11" s="5"/>
+      <c r="AC11" s="5"/>
+      <c r="AD11" s="5"/>
+      <c r="AE11" s="5"/>
+      <c r="AF11" s="5"/>
+      <c r="AG11" s="5"/>
+      <c r="AH11" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>9</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="5"/>
+      <c r="AA12" s="5"/>
+      <c r="AB12" s="5"/>
+      <c r="AC12" s="5"/>
+      <c r="AD12" s="5"/>
+      <c r="AE12" s="5"/>
+      <c r="AF12" s="5"/>
+      <c r="AG12" s="5"/>
+      <c r="AH12" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>10</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+      <c r="Z13" s="5"/>
+      <c r="AA13" s="5"/>
+      <c r="AB13" s="5"/>
+      <c r="AC13" s="5"/>
+      <c r="AD13" s="5"/>
+      <c r="AE13" s="5"/>
+      <c r="AF13" s="5"/>
+      <c r="AG13" s="5"/>
+      <c r="AH13" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>11</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5"/>
+      <c r="AA14" s="5"/>
+      <c r="AB14" s="5"/>
+      <c r="AC14" s="5"/>
+      <c r="AD14" s="5"/>
+      <c r="AE14" s="5"/>
+      <c r="AF14" s="5"/>
+      <c r="AG14" s="5"/>
+      <c r="AH14" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>12</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="5"/>
+      <c r="AA15" s="5"/>
+      <c r="AB15" s="5"/>
+      <c r="AC15" s="5"/>
+      <c r="AD15" s="5"/>
+      <c r="AE15" s="5"/>
+      <c r="AF15" s="5"/>
+      <c r="AG15" s="5"/>
+      <c r="AH15" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>13</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5"/>
+      <c r="Z16" s="5"/>
+      <c r="AA16" s="5"/>
+      <c r="AB16" s="5"/>
+      <c r="AC16" s="5"/>
+      <c r="AD16" s="5"/>
+      <c r="AE16" s="5"/>
+      <c r="AF16" s="5"/>
+      <c r="AG16" s="5"/>
+      <c r="AH16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>14</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+      <c r="W17" s="5"/>
+      <c r="X17" s="5"/>
+      <c r="Y17" s="5"/>
+      <c r="Z17" s="5"/>
+      <c r="AA17" s="5"/>
+      <c r="AB17" s="5"/>
+      <c r="AC17" s="5"/>
+      <c r="AD17" s="5"/>
+      <c r="AE17" s="5"/>
+      <c r="AF17" s="5"/>
+      <c r="AG17" s="5"/>
+      <c r="AH17" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>15</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="5"/>
+      <c r="AA18" s="5"/>
+      <c r="AB18" s="5"/>
+      <c r="AC18" s="5"/>
+      <c r="AD18" s="5"/>
+      <c r="AE18" s="5"/>
+      <c r="AF18" s="5"/>
+      <c r="AG18" s="5"/>
+      <c r="AH18" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>16</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="5"/>
+      <c r="Z19" s="5"/>
+      <c r="AA19" s="5"/>
+      <c r="AB19" s="5"/>
+      <c r="AC19" s="5"/>
+      <c r="AD19" s="5"/>
+      <c r="AE19" s="5"/>
+      <c r="AF19" s="5"/>
+      <c r="AG19" s="5"/>
+      <c r="AH19" s="5"/>
+    </row>
+    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>17</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+      <c r="X20" s="5"/>
+      <c r="Y20" s="5"/>
+      <c r="Z20" s="5"/>
+      <c r="AA20" s="5"/>
+      <c r="AB20" s="5"/>
+      <c r="AC20" s="5"/>
+      <c r="AD20" s="5"/>
+      <c r="AE20" s="5"/>
+      <c r="AF20" s="5"/>
+      <c r="AG20" s="5"/>
+      <c r="AH20" s="5"/>
+    </row>
+    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>18</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="5"/>
+      <c r="AA21" s="5"/>
+      <c r="AB21" s="5"/>
+      <c r="AC21" s="5"/>
+      <c r="AD21" s="5"/>
+      <c r="AE21" s="5"/>
+      <c r="AF21" s="5"/>
+      <c r="AG21" s="5"/>
+      <c r="AH21" s="5"/>
+    </row>
+    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>19</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="5"/>
+      <c r="Z22" s="5"/>
+      <c r="AA22" s="5"/>
+      <c r="AB22" s="5"/>
+      <c r="AC22" s="5"/>
+      <c r="AD22" s="5"/>
+      <c r="AE22" s="5"/>
+      <c r="AF22" s="5"/>
+      <c r="AG22" s="5"/>
+      <c r="AH22" s="5"/>
+    </row>
+    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>20</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="5"/>
+      <c r="W23" s="5"/>
+      <c r="X23" s="5"/>
+      <c r="Y23" s="5"/>
+      <c r="Z23" s="5"/>
+      <c r="AA23" s="5"/>
+      <c r="AB23" s="5"/>
+      <c r="AC23" s="5"/>
+      <c r="AD23" s="5"/>
+      <c r="AE23" s="5"/>
+      <c r="AF23" s="5"/>
+      <c r="AG23" s="5"/>
+      <c r="AH23" s="5"/>
+    </row>
+    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
+        <v>21</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5">
+        <v>3</v>
+      </c>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
+      <c r="V24" s="5"/>
+      <c r="W24" s="5"/>
+      <c r="X24" s="5"/>
+      <c r="Y24" s="5"/>
+      <c r="Z24" s="5"/>
+      <c r="AA24" s="5"/>
+      <c r="AB24" s="5"/>
+      <c r="AC24" s="5"/>
+      <c r="AD24" s="5"/>
+      <c r="AE24" s="5"/>
+      <c r="AF24" s="5"/>
+      <c r="AG24" s="5"/>
+      <c r="AH24" s="5">
+        <f>SUM(C24:AG24)</f>
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:AH1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:AG2"/>
+    <mergeCell ref="AH2:AH3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AH23"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1772,40 +2878,40 @@
       <c r="B1" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="30"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="30"/>
-      <c r="AE1" s="30"/>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
-      <c r="AH1" s="30" t="s">
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="26"/>
+      <c r="AB1" s="26"/>
+      <c r="AC1" s="26"/>
+      <c r="AD1" s="26"/>
+      <c r="AE1" s="26"/>
+      <c r="AF1" s="26"/>
+      <c r="AG1" s="26"/>
+      <c r="AH1" s="26" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1905,7 +3011,7 @@
       <c r="AG2" s="5">
         <v>31</v>
       </c>
-      <c r="AH2" s="30"/>
+      <c r="AH2" s="26"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
@@ -1930,7 +3036,9 @@
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
+      <c r="O3" s="5">
+        <v>20</v>
+      </c>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
@@ -1951,7 +3059,7 @@
       <c r="AG3" s="5"/>
       <c r="AH3" s="5">
         <f>SUM(C3:AG3)</f>
-        <v>24</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
@@ -2767,7 +3875,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -2817,1114 +3925,849 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AH24"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7C51F44-131D-46D9-8F20-A11BD47AE60F}">
+  <dimension ref="A1:H50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" style="8" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" style="8" customWidth="1"/>
-    <col min="3" max="34" width="5.28515625" style="8" customWidth="1"/>
-    <col min="35" max="16384" width="8.85546875" style="8"/>
+    <col min="1" max="1" width="15.7109375" style="16" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="16" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" style="16" customWidth="1"/>
+    <col min="4" max="5" width="15.7109375" style="16" customWidth="1"/>
+    <col min="6" max="6" width="21.5703125" style="16" customWidth="1"/>
+    <col min="7" max="7" width="28" style="13" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A1" s="31"/>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="31"/>
-      <c r="W1" s="31"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="31"/>
-      <c r="Z1" s="31"/>
-      <c r="AA1" s="31"/>
-      <c r="AB1" s="31"/>
-      <c r="AC1" s="31"/>
-      <c r="AD1" s="31"/>
-      <c r="AE1" s="31"/>
-      <c r="AF1" s="31"/>
-      <c r="AG1" s="31"/>
-      <c r="AH1" s="31"/>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="30"/>
-      <c r="AC2" s="30"/>
-      <c r="AD2" s="30"/>
-      <c r="AE2" s="30"/>
-      <c r="AF2" s="30"/>
-      <c r="AG2" s="30"/>
-      <c r="AH2" s="30" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="33">
+        <v>46055</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15">
+        <v>2</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="15"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="33"/>
+      <c r="B3" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="15">
+        <v>2</v>
+      </c>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="15"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="33"/>
+      <c r="B4" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15">
+        <v>1</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="15"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="33"/>
+      <c r="B5" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15">
+        <v>6</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="15"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="33">
+        <v>46056</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15">
+        <v>10</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="15"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="33"/>
+      <c r="B7" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15">
+        <v>10</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="15"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="33">
+        <v>46057</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15">
+        <v>1</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="15"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="33"/>
+      <c r="B9" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15">
+        <v>1</v>
+      </c>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="15"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="33">
+        <v>46058</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15">
+        <v>10</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="15"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="33"/>
+      <c r="B11" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17">
+        <v>20</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="15"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="33">
+        <v>46059</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15">
+        <v>1</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="15"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="33"/>
+      <c r="B13" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15">
+        <v>10</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="15"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
+        <v>46060</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15">
+        <v>6</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="15"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="33">
+        <v>46062</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15">
+        <v>20</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="15"/>
+    </row>
+    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="33"/>
+      <c r="B16" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15">
+        <v>12</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="15"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="14">
+        <v>46063</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15">
+        <v>10</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="15"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="14">
+        <v>46064</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15">
+        <v>6</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="15"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="33">
+        <v>46065</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15">
+        <v>12</v>
+      </c>
+      <c r="E19" s="15"/>
+      <c r="F19" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19" s="15"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="33"/>
+      <c r="B20" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15">
+        <v>10</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" s="15"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="30">
+        <v>46076</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15">
+        <v>1</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21" s="15"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="31"/>
+      <c r="B22" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15">
+        <v>1</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="G22" s="15"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="32"/>
+      <c r="B23" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15">
+        <v>3</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23" s="15"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="30">
+        <v>46077</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15">
+        <v>10</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="G24" s="15"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="31"/>
+      <c r="B25" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15">
+        <v>1</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="G25" s="15"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="32"/>
+      <c r="B26" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15">
+        <v>2</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="G26" s="15"/>
+    </row>
+    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="30">
+        <v>46078</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15">
+        <v>20</v>
+      </c>
+      <c r="E27" s="15">
+        <v>100</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="32"/>
+      <c r="B28" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15">
+        <v>30</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="15"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="30">
+        <v>46079</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15">
+        <v>3</v>
+      </c>
+      <c r="E29" s="15">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A3" s="30"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="5">
+      <c r="F29" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="15"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="31"/>
+      <c r="B30" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15">
         <v>1</v>
       </c>
-      <c r="D3" s="5">
+      <c r="F30" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" s="15"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="32"/>
+      <c r="B31" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15">
+        <v>20</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="G31" s="15"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="14">
+        <v>46080</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15">
+        <v>30</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="30">
+        <v>46083</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15">
+        <v>10</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G33" s="15"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="31"/>
+      <c r="B34" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15">
+        <v>10</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="G34" s="15"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="31"/>
+      <c r="B35" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15">
         <v>2</v>
       </c>
-      <c r="E3" s="5">
-        <v>3</v>
-      </c>
-      <c r="F3" s="5">
-        <v>4</v>
-      </c>
-      <c r="G3" s="5">
+      <c r="F35" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G35" s="15"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="31"/>
+      <c r="B36" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15">
+        <v>30</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="31"/>
+      <c r="B37" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15">
+        <v>1</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G37" s="15"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="32"/>
+      <c r="B38" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15">
+        <v>50</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="G38" s="15"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="14">
+        <v>46084</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15">
         <v>5</v>
       </c>
-      <c r="H3" s="5">
+      <c r="F39" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G39" s="15"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="30">
+        <v>46085</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15">
+        <v>30</v>
+      </c>
+      <c r="F40" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G40" s="15"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="32"/>
+      <c r="B41" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15">
+        <v>1</v>
+      </c>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="G41" s="15"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="14">
+        <v>46086</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15">
+        <v>20</v>
+      </c>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="G42" s="15"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="30">
+        <v>46090</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15">
+        <v>1</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G43" s="15"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="32"/>
+      <c r="B44" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15">
+        <v>1</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G44" s="15"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="14">
+        <v>46091</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15">
+        <v>10</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="G45" s="15"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="14">
+        <v>46092</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15">
         <v>6</v>
       </c>
-      <c r="I3" s="5">
-        <v>7</v>
-      </c>
-      <c r="J3" s="5">
-        <v>8</v>
-      </c>
-      <c r="K3" s="5">
-        <v>9</v>
-      </c>
-      <c r="L3" s="5">
+      <c r="F46" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="G46" s="15"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="14">
+        <v>46094</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15">
         <v>10</v>
       </c>
-      <c r="M3" s="5">
-        <v>11</v>
-      </c>
-      <c r="N3" s="5">
-        <v>12</v>
-      </c>
-      <c r="O3" s="5">
-        <v>13</v>
-      </c>
-      <c r="P3" s="5">
-        <v>14</v>
-      </c>
-      <c r="Q3" s="5">
-        <v>15</v>
-      </c>
-      <c r="R3" s="5">
-        <v>16</v>
-      </c>
-      <c r="S3" s="5">
-        <v>17</v>
-      </c>
-      <c r="T3" s="5">
-        <v>18</v>
-      </c>
-      <c r="U3" s="5">
-        <v>19</v>
-      </c>
-      <c r="V3" s="5">
-        <v>20</v>
-      </c>
-      <c r="W3" s="5">
-        <v>21</v>
-      </c>
-      <c r="X3" s="5">
-        <v>22</v>
-      </c>
-      <c r="Y3" s="5">
-        <v>23</v>
-      </c>
-      <c r="Z3" s="5">
-        <v>24</v>
-      </c>
-      <c r="AA3" s="5">
-        <v>25</v>
-      </c>
-      <c r="AB3" s="5">
-        <v>26</v>
-      </c>
-      <c r="AC3" s="5">
-        <v>27</v>
-      </c>
-      <c r="AD3" s="5">
-        <v>28</v>
-      </c>
-      <c r="AE3" s="5">
-        <v>29</v>
-      </c>
-      <c r="AF3" s="5">
-        <v>30</v>
-      </c>
-      <c r="AG3" s="5">
-        <v>31</v>
-      </c>
-      <c r="AH3" s="30"/>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5">
-        <v>1</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5">
-        <v>20</v>
-      </c>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
-      <c r="Z4" s="5"/>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="5"/>
-      <c r="AD4" s="5"/>
-      <c r="AE4" s="5"/>
-      <c r="AF4" s="5"/>
-      <c r="AG4" s="5"/>
-      <c r="AH4" s="5">
-        <f>SUM(C4:AG4)</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
-        <v>2</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5">
-        <v>3</v>
-      </c>
-      <c r="E5" s="5">
-        <v>75</v>
-      </c>
-      <c r="F5" s="5">
-        <v>186</v>
-      </c>
-      <c r="G5" s="5">
-        <v>24</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5">
-        <v>2</v>
-      </c>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5">
-        <v>16</v>
-      </c>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5"/>
-      <c r="V5" s="5"/>
-      <c r="W5" s="5"/>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="5"/>
-      <c r="Z5" s="5"/>
-      <c r="AA5" s="5"/>
-      <c r="AB5" s="5"/>
-      <c r="AC5" s="5"/>
-      <c r="AD5" s="5"/>
-      <c r="AE5" s="5"/>
-      <c r="AF5" s="5"/>
-      <c r="AG5" s="5"/>
-      <c r="AH5" s="5">
-        <f t="shared" ref="AH5:AH18" si="0">SUM(C5:AG5)</f>
-        <v>306</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
-        <v>3</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="5"/>
-      <c r="X6" s="5"/>
-      <c r="Y6" s="5"/>
-      <c r="Z6" s="5"/>
-      <c r="AA6" s="5"/>
-      <c r="AB6" s="5"/>
-      <c r="AC6" s="5"/>
-      <c r="AD6" s="5"/>
-      <c r="AE6" s="5"/>
-      <c r="AF6" s="5"/>
-      <c r="AG6" s="5"/>
-      <c r="AH6" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
-      <c r="W7" s="5"/>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="5"/>
-      <c r="Z7" s="5"/>
-      <c r="AA7" s="5"/>
-      <c r="AB7" s="5"/>
-      <c r="AC7" s="5"/>
-      <c r="AD7" s="5"/>
-      <c r="AE7" s="5"/>
-      <c r="AF7" s="5"/>
-      <c r="AG7" s="5"/>
-      <c r="AH7" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <v>5</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="5"/>
-      <c r="Z8" s="5"/>
-      <c r="AA8" s="5"/>
-      <c r="AB8" s="5"/>
-      <c r="AC8" s="5"/>
-      <c r="AD8" s="5"/>
-      <c r="AE8" s="5"/>
-      <c r="AF8" s="5"/>
-      <c r="AG8" s="5"/>
-      <c r="AH8" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
-        <v>6</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
-      <c r="U9" s="5"/>
-      <c r="V9" s="5"/>
-      <c r="W9" s="5"/>
-      <c r="X9" s="5"/>
-      <c r="Y9" s="5"/>
-      <c r="Z9" s="5"/>
-      <c r="AA9" s="5"/>
-      <c r="AB9" s="5"/>
-      <c r="AC9" s="5"/>
-      <c r="AD9" s="5"/>
-      <c r="AE9" s="5"/>
-      <c r="AF9" s="5"/>
-      <c r="AG9" s="5"/>
-      <c r="AH9" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
-        <v>7</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="5"/>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="5"/>
-      <c r="Z10" s="5"/>
-      <c r="AA10" s="5"/>
-      <c r="AB10" s="5"/>
-      <c r="AC10" s="5"/>
-      <c r="AD10" s="5"/>
-      <c r="AE10" s="5"/>
-      <c r="AF10" s="5"/>
-      <c r="AG10" s="5"/>
-      <c r="AH10" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
-        <v>8</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="5"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="5"/>
-      <c r="X11" s="5"/>
-      <c r="Y11" s="5"/>
-      <c r="Z11" s="5"/>
-      <c r="AA11" s="5"/>
-      <c r="AB11" s="5"/>
-      <c r="AC11" s="5"/>
-      <c r="AD11" s="5"/>
-      <c r="AE11" s="5"/>
-      <c r="AF11" s="5"/>
-      <c r="AG11" s="5"/>
-      <c r="AH11" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
-        <v>9</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
-      <c r="U12" s="5"/>
-      <c r="V12" s="5"/>
-      <c r="W12" s="5"/>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="5"/>
-      <c r="Z12" s="5"/>
-      <c r="AA12" s="5"/>
-      <c r="AB12" s="5"/>
-      <c r="AC12" s="5"/>
-      <c r="AD12" s="5"/>
-      <c r="AE12" s="5"/>
-      <c r="AF12" s="5"/>
-      <c r="AG12" s="5"/>
-      <c r="AH12" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A13" s="5">
-        <v>10</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="5"/>
-      <c r="V13" s="5"/>
-      <c r="W13" s="5"/>
-      <c r="X13" s="5"/>
-      <c r="Y13" s="5"/>
-      <c r="Z13" s="5"/>
-      <c r="AA13" s="5"/>
-      <c r="AB13" s="5"/>
-      <c r="AC13" s="5"/>
-      <c r="AD13" s="5"/>
-      <c r="AE13" s="5"/>
-      <c r="AF13" s="5"/>
-      <c r="AG13" s="5"/>
-      <c r="AH13" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
-        <v>11</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
-      <c r="V14" s="5"/>
-      <c r="W14" s="5"/>
-      <c r="X14" s="5"/>
-      <c r="Y14" s="5"/>
-      <c r="Z14" s="5"/>
-      <c r="AA14" s="5"/>
-      <c r="AB14" s="5"/>
-      <c r="AC14" s="5"/>
-      <c r="AD14" s="5"/>
-      <c r="AE14" s="5"/>
-      <c r="AF14" s="5"/>
-      <c r="AG14" s="5"/>
-      <c r="AH14" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A15" s="5">
-        <v>12</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="5"/>
-      <c r="V15" s="5"/>
-      <c r="W15" s="5"/>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5"/>
-      <c r="Z15" s="5"/>
-      <c r="AA15" s="5"/>
-      <c r="AB15" s="5"/>
-      <c r="AC15" s="5"/>
-      <c r="AD15" s="5"/>
-      <c r="AE15" s="5"/>
-      <c r="AF15" s="5"/>
-      <c r="AG15" s="5"/>
-      <c r="AH15" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
-        <v>13</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
-      <c r="U16" s="5"/>
-      <c r="V16" s="5"/>
-      <c r="W16" s="5"/>
-      <c r="X16" s="5"/>
-      <c r="Y16" s="5"/>
-      <c r="Z16" s="5"/>
-      <c r="AA16" s="5"/>
-      <c r="AB16" s="5"/>
-      <c r="AC16" s="5"/>
-      <c r="AD16" s="5"/>
-      <c r="AE16" s="5"/>
-      <c r="AF16" s="5"/>
-      <c r="AG16" s="5"/>
-      <c r="AH16" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
-        <v>14</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
-      <c r="T17" s="5"/>
-      <c r="U17" s="5"/>
-      <c r="V17" s="5"/>
-      <c r="W17" s="5"/>
-      <c r="X17" s="5"/>
-      <c r="Y17" s="5"/>
-      <c r="Z17" s="5"/>
-      <c r="AA17" s="5"/>
-      <c r="AB17" s="5"/>
-      <c r="AC17" s="5"/>
-      <c r="AD17" s="5"/>
-      <c r="AE17" s="5"/>
-      <c r="AF17" s="5"/>
-      <c r="AG17" s="5"/>
-      <c r="AH17" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
-        <v>15</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-      <c r="U18" s="5"/>
-      <c r="V18" s="5"/>
-      <c r="W18" s="5"/>
-      <c r="X18" s="5"/>
-      <c r="Y18" s="5"/>
-      <c r="Z18" s="5"/>
-      <c r="AA18" s="5"/>
-      <c r="AB18" s="5"/>
-      <c r="AC18" s="5"/>
-      <c r="AD18" s="5"/>
-      <c r="AE18" s="5"/>
-      <c r="AF18" s="5"/>
-      <c r="AG18" s="5"/>
-      <c r="AH18" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A19" s="5">
-        <v>16</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="5"/>
-      <c r="V19" s="5"/>
-      <c r="W19" s="5"/>
-      <c r="X19" s="5"/>
-      <c r="Y19" s="5"/>
-      <c r="Z19" s="5"/>
-      <c r="AA19" s="5"/>
-      <c r="AB19" s="5"/>
-      <c r="AC19" s="5"/>
-      <c r="AD19" s="5"/>
-      <c r="AE19" s="5"/>
-      <c r="AF19" s="5"/>
-      <c r="AG19" s="5"/>
-      <c r="AH19" s="5"/>
-    </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A20" s="5">
-        <v>17</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
-      <c r="V20" s="5"/>
-      <c r="W20" s="5"/>
-      <c r="X20" s="5"/>
-      <c r="Y20" s="5"/>
-      <c r="Z20" s="5"/>
-      <c r="AA20" s="5"/>
-      <c r="AB20" s="5"/>
-      <c r="AC20" s="5"/>
-      <c r="AD20" s="5"/>
-      <c r="AE20" s="5"/>
-      <c r="AF20" s="5"/>
-      <c r="AG20" s="5"/>
-      <c r="AH20" s="5"/>
-    </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A21" s="5">
-        <v>18</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="5"/>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
-      <c r="X21" s="5"/>
-      <c r="Y21" s="5"/>
-      <c r="Z21" s="5"/>
-      <c r="AA21" s="5"/>
-      <c r="AB21" s="5"/>
-      <c r="AC21" s="5"/>
-      <c r="AD21" s="5"/>
-      <c r="AE21" s="5"/>
-      <c r="AF21" s="5"/>
-      <c r="AG21" s="5"/>
-      <c r="AH21" s="5"/>
-    </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A22" s="5">
-        <v>19</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="5"/>
-      <c r="W22" s="5"/>
-      <c r="X22" s="5"/>
-      <c r="Y22" s="5"/>
-      <c r="Z22" s="5"/>
-      <c r="AA22" s="5"/>
-      <c r="AB22" s="5"/>
-      <c r="AC22" s="5"/>
-      <c r="AD22" s="5"/>
-      <c r="AE22" s="5"/>
-      <c r="AF22" s="5"/>
-      <c r="AG22" s="5"/>
-      <c r="AH22" s="5"/>
-    </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A23" s="5">
-        <v>20</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
-      <c r="U23" s="5"/>
-      <c r="V23" s="5"/>
-      <c r="W23" s="5"/>
-      <c r="X23" s="5"/>
-      <c r="Y23" s="5"/>
-      <c r="Z23" s="5"/>
-      <c r="AA23" s="5"/>
-      <c r="AB23" s="5"/>
-      <c r="AC23" s="5"/>
-      <c r="AD23" s="5"/>
-      <c r="AE23" s="5"/>
-      <c r="AF23" s="5"/>
-      <c r="AG23" s="5"/>
-      <c r="AH23" s="5"/>
-    </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A24" s="5">
-        <v>21</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5">
-        <v>3</v>
-      </c>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
-      <c r="U24" s="5"/>
-      <c r="V24" s="5"/>
-      <c r="W24" s="5"/>
-      <c r="X24" s="5"/>
-      <c r="Y24" s="5"/>
-      <c r="Z24" s="5"/>
-      <c r="AA24" s="5"/>
-      <c r="AB24" s="5"/>
-      <c r="AC24" s="5"/>
-      <c r="AD24" s="5"/>
-      <c r="AE24" s="5"/>
-      <c r="AF24" s="5"/>
-      <c r="AG24" s="5"/>
-      <c r="AH24" s="5">
-        <f>SUM(C24:AG24)</f>
-        <v>3</v>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="G47" s="15"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="15"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="15"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="15"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="15"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D50" s="16">
+        <f>SUM(D2:D32)</f>
+        <v>38</v>
+      </c>
+      <c r="E50" s="16">
+        <f>SUM(E2:E32)</f>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:AH1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:AG2"/>
-    <mergeCell ref="AH2:AH3"/>
+  <autoFilter ref="A1:F38" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
+  <mergeCells count="14">
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A33:A38"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
   </mergeCells>
+  <conditionalFormatting sqref="D2:F1000">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>ISNUMBER(SEARCH("Đã trả",$F2))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>ISNUMBER(SEARCH("Chưa trả",$F2))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AH22"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3936,52 +4779,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="30"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="30"/>
-      <c r="AE1" s="30"/>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
-      <c r="AH1" s="30" t="s">
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="26"/>
+      <c r="AB1" s="26"/>
+      <c r="AC1" s="26"/>
+      <c r="AD1" s="26"/>
+      <c r="AE1" s="26"/>
+      <c r="AF1" s="26"/>
+      <c r="AG1" s="26"/>
+      <c r="AH1" s="26" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
       <c r="C2" s="5">
         <v>1</v>
       </c>
@@ -4075,7 +4918,7 @@
       <c r="AG2" s="5">
         <v>31</v>
       </c>
-      <c r="AH2" s="30"/>
+      <c r="AH2" s="26"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
@@ -4928,840 +5771,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7C51F44-131D-46D9-8F20-A11BD47AE60F}">
-  <dimension ref="A1:H50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.7109375" style="17" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" style="17" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" style="17" customWidth="1"/>
-    <col min="4" max="5" width="15.7109375" style="17" customWidth="1"/>
-    <col min="6" max="6" width="21.5703125" style="17" customWidth="1"/>
-    <col min="7" max="7" width="28" style="13" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="35">
-        <v>46055</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15">
-        <v>2</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" s="16"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="35"/>
-      <c r="B3" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="15">
-        <v>2</v>
-      </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="16"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15">
-        <v>1</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="16"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="35"/>
-      <c r="B5" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15">
-        <v>6</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="16"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="35">
-        <v>46056</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15">
-        <v>10</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="16"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="35"/>
-      <c r="B7" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15">
-        <v>10</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="16"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="35">
-        <v>46057</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15">
-        <v>1</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" s="16"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="35"/>
-      <c r="B9" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15">
-        <v>1</v>
-      </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="16"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="35">
-        <v>46058</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15">
-        <v>10</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="16"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="35"/>
-      <c r="B11" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18">
-        <v>20</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" s="16"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="35">
-        <v>46059</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15">
-        <v>1</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" s="16"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
-      <c r="B13" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15">
-        <v>10</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13" s="16"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="14">
-        <v>46060</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15">
-        <v>6</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14" s="16"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="35">
-        <v>46062</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15">
-        <v>20</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15" s="16"/>
-    </row>
-    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="35"/>
-      <c r="B16" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15">
-        <v>12</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="G16" s="16"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="14">
-        <v>46063</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15">
-        <v>10</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17" s="16"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="14">
-        <v>46064</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15">
-        <v>6</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G18" s="16"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="35">
-        <v>46065</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15">
-        <v>12</v>
-      </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="G19" s="16"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="35"/>
-      <c r="B20" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15">
-        <v>10</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="G20" s="16"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="32">
-        <v>46076</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15">
-        <v>1</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G21" s="16"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="33"/>
-      <c r="B22" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15">
-        <v>1</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G22" s="16"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="34"/>
-      <c r="B23" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15">
-        <v>3</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G23" s="16"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="32">
-        <v>46077</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15">
-        <v>10</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="16"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="33"/>
-      <c r="B25" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15">
-        <v>1</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G25" s="16"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="34"/>
-      <c r="B26" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15">
-        <v>2</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G26" s="16"/>
-    </row>
-    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="32">
-        <v>46078</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15">
-        <v>20</v>
-      </c>
-      <c r="E27" s="15">
-        <v>100</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="G27" s="16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
-      <c r="B28" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15">
-        <v>30</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G28" s="16"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="32">
-        <v>46079</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15">
-        <v>3</v>
-      </c>
-      <c r="E29" s="15">
-        <v>5</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G29" s="16"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="33"/>
-      <c r="B30" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15">
-        <v>1</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G30" s="16"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="34"/>
-      <c r="B31" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15">
-        <v>20</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="G31" s="16"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="14">
-        <v>46080</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15">
-        <v>30</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="G32" s="16" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="32">
-        <v>46083</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15">
-        <v>10</v>
-      </c>
-      <c r="F33" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="G33" s="16"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="33"/>
-      <c r="B34" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15">
-        <v>10</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="G34" s="16"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="33"/>
-      <c r="B35" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15">
-        <v>2</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="G35" s="16"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="33"/>
-      <c r="B36" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15">
-        <v>30</v>
-      </c>
-      <c r="F36" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="G36" s="16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="33"/>
-      <c r="B37" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15">
-        <v>1</v>
-      </c>
-      <c r="F37" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="G37" s="16"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="34"/>
-      <c r="B38" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15">
-        <v>50</v>
-      </c>
-      <c r="F38" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="G38" s="16"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="14">
-        <v>46084</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15">
-        <v>5</v>
-      </c>
-      <c r="F39" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="G39" s="16"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="32">
-        <v>46085</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15">
-        <v>30</v>
-      </c>
-      <c r="F40" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="G40" s="16"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="34"/>
-      <c r="B41" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15">
-        <v>1</v>
-      </c>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="G41" s="16"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="14">
-        <v>46086</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15">
-        <v>20</v>
-      </c>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="G42" s="16"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="32">
-        <v>46090</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15">
-        <v>1</v>
-      </c>
-      <c r="F43" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="G43" s="16"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="34"/>
-      <c r="B44" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15">
-        <v>1</v>
-      </c>
-      <c r="F44" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="G44" s="16"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="14">
-        <v>46091</v>
-      </c>
-      <c r="B45" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15">
-        <v>10</v>
-      </c>
-      <c r="F45" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="G45" s="16"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="14">
-        <v>46092</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15">
-        <v>6</v>
-      </c>
-      <c r="F46" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="G46" s="16"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="15"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="16"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="15"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="16"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="15"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="16"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D50" s="17">
-        <f>SUM(D2:D32)</f>
-        <v>38</v>
-      </c>
-      <c r="E50" s="17">
-        <f>SUM(E2:E32)</f>
-        <v>339</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F38" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
-  <mergeCells count="14">
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A33:A38"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-  </mergeCells>
-  <conditionalFormatting sqref="D2:F1000">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>ISNUMBER(SEARCH("Đã trả",$F2))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>ISNUMBER(SEARCH("Chưa trả",$F2))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B1D2FD3-91FF-42CA-8178-C2AD22F246DD}">
   <dimension ref="A1:H20"/>
@@ -5774,40 +5783,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="25"/>
+      <c r="A1" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="18" t="s">
         <v>11</v>
       </c>
     </row>
@@ -5824,15 +5833,15 @@
       </c>
       <c r="D3" s="3">
         <f>SUM('Nhập xuất tồn'!D3)</f>
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E3" s="3">
         <f>SUM('Nhập xuất tồn'!E3)</f>
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F3" s="3">
         <f>SUM(C3+D3-E3)</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G3" s="4">
         <f>'Nhập xuất tồn'!G3</f>
@@ -5840,7 +5849,7 @@
       </c>
       <c r="H3" s="3">
         <f>SUM(F3-G3)</f>
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -6273,7 +6282,7 @@
         <v>21</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C18" s="3">
         <f>'Nhập xuất tồn'!C23</f>
@@ -6301,25 +6310,25 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="36"/>
+      <c r="B19" s="34"/>
       <c r="C19" s="10">
         <f>SUM(C3:C17)</f>
         <v>134</v>
       </c>
       <c r="D19" s="10">
         <f>SUM(D3:D17)</f>
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="E19" s="10">
         <f>SUM(E3:E17)</f>
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
@@ -6327,7 +6336,7 @@
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5F5EB6-8D1E-4E6F-8DE2-2D71E33DB29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6679C52E-754D-49C2-88A0-B00A79262EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="90">
   <si>
     <t>VNSH01</t>
   </si>
@@ -305,7 +305,7 @@
     <t>Danh Sách Thiết Bị Gửi Trên Bảo Hành - Sản Xuất Tháng 03</t>
   </si>
   <si>
-    <t>Chưa trả</t>
+    <t>Đã trả (13/03/26)</t>
   </si>
 </sst>
 </file>
@@ -567,10 +567,10 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1074,18 +1074,18 @@
       </c>
       <c r="E3" s="3">
         <f>Xuất!AH4+Huỷ!AH3</f>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F3" s="3">
         <f>C3+D3-E3</f>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3" s="4">
         <v>2</v>
       </c>
       <c r="H3" s="3">
         <f>F3-G3</f>
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1708,11 +1708,11 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="H24" s="3">
         <f>SUM(H3:H23)</f>
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1964,7 +1964,7 @@
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
@@ -1986,7 +1986,7 @@
       <c r="AG4" s="5"/>
       <c r="AH4" s="5">
         <f>SUM(C4:AG4)</f>
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
@@ -4286,7 +4286,7 @@
       <c r="G21" s="15"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="31"/>
+      <c r="A22" s="32"/>
       <c r="B22" s="15" t="s">
         <v>64</v>
       </c>
@@ -4301,7 +4301,7 @@
       <c r="G22" s="15"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="32"/>
+      <c r="A23" s="31"/>
       <c r="B23" s="15" t="s">
         <v>66</v>
       </c>
@@ -4333,7 +4333,7 @@
       <c r="G24" s="15"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="31"/>
+      <c r="A25" s="32"/>
       <c r="B25" s="15" t="s">
         <v>63</v>
       </c>
@@ -4348,7 +4348,7 @@
       <c r="G25" s="15"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="32"/>
+      <c r="A26" s="31"/>
       <c r="B26" s="15" t="s">
         <v>14</v>
       </c>
@@ -4384,7 +4384,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="32"/>
+      <c r="A28" s="31"/>
       <c r="B28" s="15" t="s">
         <v>49</v>
       </c>
@@ -4418,7 +4418,7 @@
       <c r="G29" s="15"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="31"/>
+      <c r="A30" s="32"/>
       <c r="B30" s="15" t="s">
         <v>69</v>
       </c>
@@ -4433,7 +4433,7 @@
       <c r="G30" s="15"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="32"/>
+      <c r="A31" s="31"/>
       <c r="B31" s="15" t="s">
         <v>49</v>
       </c>
@@ -4484,7 +4484,7 @@
       <c r="G33" s="15"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="31"/>
+      <c r="A34" s="32"/>
       <c r="B34" s="15" t="s">
         <v>49</v>
       </c>
@@ -4499,7 +4499,7 @@
       <c r="G34" s="15"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="31"/>
+      <c r="A35" s="32"/>
       <c r="B35" s="15" t="s">
         <v>14</v>
       </c>
@@ -4514,7 +4514,7 @@
       <c r="G35" s="15"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="31"/>
+      <c r="A36" s="32"/>
       <c r="B36" s="15" t="s">
         <v>74</v>
       </c>
@@ -4531,7 +4531,7 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="31"/>
+      <c r="A37" s="32"/>
       <c r="B37" s="15" t="s">
         <v>75</v>
       </c>
@@ -4546,7 +4546,7 @@
       <c r="G37" s="15"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="32"/>
+      <c r="A38" s="31"/>
       <c r="B38" s="15" t="s">
         <v>61</v>
       </c>
@@ -4595,7 +4595,7 @@
       <c r="G40" s="15"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="32"/>
+      <c r="A41" s="31"/>
       <c r="B41" s="15" t="s">
         <v>80</v>
       </c>
@@ -4644,7 +4644,7 @@
       <c r="G43" s="15"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="32"/>
+      <c r="A44" s="31"/>
       <c r="B44" s="15" t="s">
         <v>84</v>
       </c>
@@ -4693,7 +4693,7 @@
       <c r="G46" s="15"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="14">
+      <c r="A47" s="30">
         <v>46094</v>
       </c>
       <c r="B47" s="15" t="s">
@@ -4710,12 +4710,18 @@
       <c r="G47" s="15"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="15"/>
-      <c r="B48" s="15"/>
+      <c r="A48" s="31"/>
+      <c r="B48" s="15" t="s">
+        <v>74</v>
+      </c>
       <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
+      <c r="D48" s="15">
+        <v>3</v>
+      </c>
       <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
+      <c r="F48" s="15" t="s">
+        <v>89</v>
+      </c>
       <c r="G48" s="15"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -4739,12 +4745,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F38" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
-  <mergeCells count="14">
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A33:A38"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A24:A26"/>
+  <mergeCells count="15">
+    <mergeCell ref="A47:A48"/>
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A29:A31"/>
@@ -4754,6 +4756,11 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A33:A38"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A24:A26"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:F1000">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -5837,11 +5844,11 @@
       </c>
       <c r="E3" s="3">
         <f>SUM('Nhập xuất tồn'!E3)</f>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F3" s="3">
         <f>SUM(C3+D3-E3)</f>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3" s="4">
         <f>'Nhập xuất tồn'!G3</f>
@@ -5849,7 +5856,7 @@
       </c>
       <c r="H3" s="3">
         <f>SUM(F3-G3)</f>
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -6324,11 +6331,11 @@
       </c>
       <c r="E19" s="10">
         <f>SUM(E3:E17)</f>
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
@@ -6336,7 +6343,7 @@
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6679C52E-754D-49C2-88A0-B00A79262EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6351C078-7DA7-46E1-997E-13FB8A404FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="91">
   <si>
     <t>VNSH01</t>
   </si>
@@ -306,6 +306,9 @@
   </si>
   <si>
     <t>Đã trả (13/03/26)</t>
+  </si>
+  <si>
+    <t>Chưa trả</t>
   </si>
 </sst>
 </file>
@@ -1070,7 +1073,7 @@
       </c>
       <c r="D3" s="3">
         <f>Nhập!AH3</f>
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3">
         <f>Xuất!AH4+Huỷ!AH3</f>
@@ -1078,14 +1081,14 @@
       </c>
       <c r="F3" s="3">
         <f>C3+D3-E3</f>
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G3" s="4">
         <v>2</v>
       </c>
       <c r="H3" s="3">
         <f>F3-G3</f>
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1101,7 +1104,7 @@
       </c>
       <c r="D4" s="3">
         <f>Nhập!AH4</f>
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E4" s="3">
         <f>Xuất!AH5+Huỷ!AH4</f>
@@ -1109,7 +1112,7 @@
       </c>
       <c r="F4" s="3">
         <f>C4+D4-E4</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="3"/>
@@ -1704,7 +1707,7 @@
       </c>
       <c r="D24" s="3">
         <f t="shared" ref="D24:G24" si="2">SUM(D3:D22)</f>
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
@@ -1712,7 +1715,7 @@
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
@@ -1720,7 +1723,7 @@
       </c>
       <c r="H24" s="3">
         <f>SUM(H3:H23)</f>
-        <v>20</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -3043,7 +3046,9 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
       <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
+      <c r="T3" s="5">
+        <v>21</v>
+      </c>
       <c r="U3" s="5"/>
       <c r="V3" s="5"/>
       <c r="W3" s="5"/>
@@ -3059,7 +3064,7 @@
       <c r="AG3" s="5"/>
       <c r="AH3" s="5">
         <f>SUM(C3:AG3)</f>
-        <v>44</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
@@ -3092,7 +3097,9 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
+      <c r="T4" s="5">
+        <v>1</v>
+      </c>
       <c r="U4" s="5"/>
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
@@ -3108,7 +3115,7 @@
       <c r="AG4" s="5"/>
       <c r="AH4" s="5">
         <f t="shared" ref="AH4:AH19" si="0">SUM(C4:AG4)</f>
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
@@ -4725,12 +4732,20 @@
       <c r="G48" s="15"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="15"/>
-      <c r="B49" s="15"/>
+      <c r="A49" s="14">
+        <v>46099</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>49</v>
+      </c>
       <c r="C49" s="15"/>
       <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
+      <c r="E49" s="15">
+        <v>10</v>
+      </c>
+      <c r="F49" s="15" t="s">
+        <v>90</v>
+      </c>
       <c r="G49" s="15"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -4746,16 +4761,16 @@
   </sheetData>
   <autoFilter ref="A1:F38" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
   <mergeCells count="15">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="A33:A38"/>
@@ -5840,7 +5855,7 @@
       </c>
       <c r="D3" s="3">
         <f>SUM('Nhập xuất tồn'!D3)</f>
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3">
         <f>SUM('Nhập xuất tồn'!E3)</f>
@@ -5848,7 +5863,7 @@
       </c>
       <c r="F3" s="3">
         <f>SUM(C3+D3-E3)</f>
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G3" s="4">
         <f>'Nhập xuất tồn'!G3</f>
@@ -5856,7 +5871,7 @@
       </c>
       <c r="H3" s="3">
         <f>SUM(F3-G3)</f>
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -5872,7 +5887,7 @@
       </c>
       <c r="D4" s="3">
         <f>SUM('Nhập xuất tồn'!D4)</f>
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E4" s="3">
         <f>SUM('Nhập xuất tồn'!E4)</f>
@@ -5880,7 +5895,7 @@
       </c>
       <c r="F4" s="3">
         <f>SUM(C4+D4-E4)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" s="4">
         <f>'Nhập xuất tồn'!G4</f>
@@ -5888,7 +5903,7 @@
       </c>
       <c r="H4" s="3">
         <f>SUM(F4-G4)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -6327,7 +6342,7 @@
       </c>
       <c r="D19" s="10">
         <f>SUM(D3:D17)</f>
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="E19" s="10">
         <f>SUM(E3:E17)</f>
@@ -6335,7 +6350,7 @@
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
@@ -6343,7 +6358,7 @@
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>46</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6351C078-7DA7-46E1-997E-13FB8A404FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB39FBA-2B20-4E81-A5CD-A34A3EE1B1F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="4365" windowWidth="21600" windowHeight="11835" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
   <si>
     <t>VNSH01</t>
   </si>
@@ -306,6 +306,9 @@
   </si>
   <si>
     <t>Đã trả (13/03/26)</t>
+  </si>
+  <si>
+    <t>Đã trả (19/03/26)</t>
   </si>
   <si>
     <t>Chưa trả</t>
@@ -478,7 +481,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -540,6 +543,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -570,10 +576,10 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1023,16 +1029,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="23"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -1077,18 +1083,18 @@
       </c>
       <c r="E3" s="3">
         <f>Xuất!AH4+Huỷ!AH3</f>
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F3" s="3">
         <f>C3+D3-E3</f>
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G3" s="4">
         <v>2</v>
       </c>
       <c r="H3" s="3">
         <f>F3-G3</f>
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1697,10 +1703,10 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="24"/>
+      <c r="B24" s="25"/>
       <c r="C24" s="3">
         <f>SUM(C3:C22)</f>
         <v>134</v>
@@ -1711,11 +1717,11 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
@@ -1723,7 +1729,7 @@
       </c>
       <c r="H24" s="3">
         <f>SUM(H3:H23)</f>
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1766,88 +1772,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A1" s="25"/>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="25"/>
-      <c r="AC1" s="25"/>
-      <c r="AD1" s="25"/>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="25"/>
-      <c r="AH1" s="25"/>
+      <c r="A1" s="26"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="26"/>
+      <c r="AB1" s="26"/>
+      <c r="AC1" s="26"/>
+      <c r="AD1" s="26"/>
+      <c r="AE1" s="26"/>
+      <c r="AF1" s="26"/>
+      <c r="AG1" s="26"/>
+      <c r="AH1" s="26"/>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="26"/>
-      <c r="Y2" s="26"/>
-      <c r="Z2" s="26"/>
-      <c r="AA2" s="26"/>
-      <c r="AB2" s="26"/>
-      <c r="AC2" s="26"/>
-      <c r="AD2" s="26"/>
-      <c r="AE2" s="26"/>
-      <c r="AF2" s="26"/>
-      <c r="AG2" s="26"/>
-      <c r="AH2" s="26" t="s">
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="27"/>
+      <c r="AC2" s="27"/>
+      <c r="AD2" s="27"/>
+      <c r="AE2" s="27"/>
+      <c r="AF2" s="27"/>
+      <c r="AG2" s="27"/>
+      <c r="AH2" s="27" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
+      <c r="A3" s="27"/>
+      <c r="B3" s="27"/>
       <c r="C3" s="5">
         <v>1</v>
       </c>
@@ -1941,7 +1947,7 @@
       <c r="AG3" s="5">
         <v>31</v>
       </c>
-      <c r="AH3" s="26"/>
+      <c r="AH3" s="27"/>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
@@ -1974,7 +1980,9 @@
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
+      <c r="U4" s="5">
+        <v>10</v>
+      </c>
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
@@ -1989,7 +1997,7 @@
       <c r="AG4" s="5"/>
       <c r="AH4" s="5">
         <f>SUM(C4:AG4)</f>
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
@@ -2875,52 +2883,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="26"/>
-      <c r="AB1" s="26"/>
-      <c r="AC1" s="26"/>
-      <c r="AD1" s="26"/>
-      <c r="AE1" s="26"/>
-      <c r="AF1" s="26"/>
-      <c r="AG1" s="26"/>
-      <c r="AH1" s="26" t="s">
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="27"/>
+      <c r="AC1" s="27"/>
+      <c r="AD1" s="27"/>
+      <c r="AE1" s="27"/>
+      <c r="AF1" s="27"/>
+      <c r="AG1" s="27"/>
+      <c r="AH1" s="27" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" s="27"/>
-      <c r="B2" s="29"/>
+      <c r="A2" s="28"/>
+      <c r="B2" s="30"/>
       <c r="C2" s="5">
         <v>1</v>
       </c>
@@ -3014,7 +3022,7 @@
       <c r="AG2" s="5">
         <v>31</v>
       </c>
-      <c r="AH2" s="26"/>
+      <c r="AH2" s="27"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
@@ -3934,7 +3942,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7C51F44-131D-46D9-8F20-A11BD47AE60F}">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="16" customWidth="1"/>
@@ -3971,7 +3979,7 @@
       <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="33">
+      <c r="A2" s="34">
         <v>46055</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -3988,7 +3996,7 @@
       <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="33"/>
+      <c r="A3" s="34"/>
       <c r="B3" s="15" t="s">
         <v>39</v>
       </c>
@@ -4003,7 +4011,7 @@
       <c r="G3" s="15"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="33"/>
+      <c r="A4" s="34"/>
       <c r="B4" s="15" t="s">
         <v>40</v>
       </c>
@@ -4018,7 +4026,7 @@
       <c r="G4" s="15"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="33"/>
+      <c r="A5" s="34"/>
       <c r="B5" s="15" t="s">
         <v>41</v>
       </c>
@@ -4033,7 +4041,7 @@
       <c r="G5" s="15"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="33">
+      <c r="A6" s="34">
         <v>46056</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -4050,7 +4058,7 @@
       <c r="G6" s="15"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="33"/>
+      <c r="A7" s="34"/>
       <c r="B7" s="15" t="s">
         <v>43</v>
       </c>
@@ -4065,7 +4073,7 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="33">
+      <c r="A8" s="34">
         <v>46057</v>
       </c>
       <c r="B8" s="14" t="s">
@@ -4082,7 +4090,7 @@
       <c r="G8" s="15"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="33"/>
+      <c r="A9" s="34"/>
       <c r="B9" s="15" t="s">
         <v>39</v>
       </c>
@@ -4097,7 +4105,7 @@
       <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="33">
+      <c r="A10" s="34">
         <v>46058</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -4114,7 +4122,7 @@
       <c r="G10" s="15"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
+      <c r="A11" s="34"/>
       <c r="B11" s="15" t="s">
         <v>49</v>
       </c>
@@ -4129,7 +4137,7 @@
       <c r="G11" s="15"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="33">
+      <c r="A12" s="34">
         <v>46059</v>
       </c>
       <c r="B12" s="15" t="s">
@@ -4146,7 +4154,7 @@
       <c r="G12" s="15"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="33"/>
+      <c r="A13" s="34"/>
       <c r="B13" s="15" t="s">
         <v>50</v>
       </c>
@@ -4178,7 +4186,7 @@
       <c r="G14" s="15"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="33">
+      <c r="A15" s="34">
         <v>46062</v>
       </c>
       <c r="B15" s="15" t="s">
@@ -4195,7 +4203,7 @@
       <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
+      <c r="A16" s="34"/>
       <c r="B16" s="15" t="s">
         <v>41</v>
       </c>
@@ -4244,7 +4252,7 @@
       <c r="G18" s="15"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="33">
+      <c r="A19" s="34">
         <v>46065</v>
       </c>
       <c r="B19" s="15" t="s">
@@ -4261,7 +4269,7 @@
       <c r="G19" s="15"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="33"/>
+      <c r="A20" s="34"/>
       <c r="B20" s="15" t="s">
         <v>49</v>
       </c>
@@ -4276,7 +4284,7 @@
       <c r="G20" s="15"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="30">
+      <c r="A21" s="31">
         <v>46076</v>
       </c>
       <c r="B21" s="15" t="s">
@@ -4308,7 +4316,7 @@
       <c r="G22" s="15"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="31"/>
+      <c r="A23" s="33"/>
       <c r="B23" s="15" t="s">
         <v>66</v>
       </c>
@@ -4323,7 +4331,7 @@
       <c r="G23" s="15"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="30">
+      <c r="A24" s="31">
         <v>46077</v>
       </c>
       <c r="B24" s="15" t="s">
@@ -4355,7 +4363,7 @@
       <c r="G25" s="15"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="31"/>
+      <c r="A26" s="33"/>
       <c r="B26" s="15" t="s">
         <v>14</v>
       </c>
@@ -4370,7 +4378,7 @@
       <c r="G26" s="15"/>
     </row>
     <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="30">
+      <c r="A27" s="31">
         <v>46078</v>
       </c>
       <c r="B27" s="15" t="s">
@@ -4391,7 +4399,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="31"/>
+      <c r="A28" s="33"/>
       <c r="B28" s="15" t="s">
         <v>49</v>
       </c>
@@ -4406,7 +4414,7 @@
       <c r="G28" s="15"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="30">
+      <c r="A29" s="31">
         <v>46079</v>
       </c>
       <c r="B29" s="15" t="s">
@@ -4440,7 +4448,7 @@
       <c r="G30" s="15"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="31"/>
+      <c r="A31" s="33"/>
       <c r="B31" s="15" t="s">
         <v>49</v>
       </c>
@@ -4474,7 +4482,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="30">
+      <c r="A33" s="31">
         <v>46083</v>
       </c>
       <c r="B33" s="15" t="s">
@@ -4553,7 +4561,7 @@
       <c r="G37" s="15"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="31"/>
+      <c r="A38" s="33"/>
       <c r="B38" s="15" t="s">
         <v>61</v>
       </c>
@@ -4585,7 +4593,7 @@
       <c r="G39" s="15"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="30">
+      <c r="A40" s="31">
         <v>46085</v>
       </c>
       <c r="B40" s="15" t="s">
@@ -4602,7 +4610,7 @@
       <c r="G40" s="15"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="31"/>
+      <c r="A41" s="33"/>
       <c r="B41" s="15" t="s">
         <v>80</v>
       </c>
@@ -4634,7 +4642,7 @@
       <c r="G42" s="15"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="30">
+      <c r="A43" s="31">
         <v>46090</v>
       </c>
       <c r="B43" s="15" t="s">
@@ -4651,7 +4659,7 @@
       <c r="G43" s="15"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="31"/>
+      <c r="A44" s="33"/>
       <c r="B44" s="15" t="s">
         <v>84</v>
       </c>
@@ -4700,7 +4708,7 @@
       <c r="G46" s="15"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="30">
+      <c r="A47" s="34">
         <v>46094</v>
       </c>
       <c r="B47" s="15" t="s">
@@ -4717,7 +4725,7 @@
       <c r="G47" s="15"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="31"/>
+      <c r="A48" s="34"/>
       <c r="B48" s="15" t="s">
         <v>74</v>
       </c>
@@ -4749,33 +4757,233 @@
       <c r="G49" s="15"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D50" s="16">
-        <f>SUM(D2:D32)</f>
-        <v>38</v>
-      </c>
-      <c r="E50" s="16">
-        <f>SUM(E2:E32)</f>
-        <v>339</v>
-      </c>
+      <c r="A50" s="31">
+        <v>46101</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15">
+        <v>20</v>
+      </c>
+      <c r="F50" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G50" s="21"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="32"/>
+      <c r="B51" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15">
+        <v>9</v>
+      </c>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G51" s="21"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="33"/>
+      <c r="B52" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15">
+        <v>25</v>
+      </c>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G52" s="21"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="15"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="21"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="15"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="21"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="15"/>
+      <c r="B55" s="15"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="21"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="15"/>
+      <c r="B56" s="15"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="21"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="15"/>
+      <c r="B57" s="15"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="21"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="15"/>
+      <c r="B58" s="15"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="21"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="15"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="21"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="15"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="21"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="15"/>
+      <c r="B61" s="15"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="15"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="15"/>
+      <c r="G61" s="21"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="15"/>
+      <c r="B62" s="15"/>
+      <c r="C62" s="15"/>
+      <c r="D62" s="15"/>
+      <c r="E62" s="15"/>
+      <c r="F62" s="15"/>
+      <c r="G62" s="21"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="15"/>
+      <c r="B63" s="15"/>
+      <c r="C63" s="15"/>
+      <c r="D63" s="15"/>
+      <c r="E63" s="15"/>
+      <c r="F63" s="15"/>
+      <c r="G63" s="21"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="15"/>
+      <c r="B64" s="15"/>
+      <c r="C64" s="15"/>
+      <c r="D64" s="15"/>
+      <c r="E64" s="15"/>
+      <c r="F64" s="15"/>
+      <c r="G64" s="21"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="15"/>
+      <c r="B65" s="15"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="15"/>
+      <c r="E65" s="15"/>
+      <c r="F65" s="15"/>
+      <c r="G65" s="21"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="15"/>
+      <c r="B66" s="15"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="15"/>
+      <c r="G66" s="21"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="15"/>
+      <c r="B67" s="15"/>
+      <c r="C67" s="15"/>
+      <c r="D67" s="15"/>
+      <c r="E67" s="15"/>
+      <c r="F67" s="15"/>
+      <c r="G67" s="21"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="15"/>
+      <c r="B68" s="15"/>
+      <c r="C68" s="15"/>
+      <c r="D68" s="15"/>
+      <c r="E68" s="15"/>
+      <c r="F68" s="15"/>
+      <c r="G68" s="21"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="15"/>
+      <c r="B69" s="15"/>
+      <c r="C69" s="15"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="15"/>
+      <c r="F69" s="15"/>
+      <c r="G69" s="21"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="15"/>
+      <c r="B70" s="15"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="21"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F38" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A29:A31"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="A33:A38"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A29:A31"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:F1000">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -4801,52 +5009,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="26"/>
-      <c r="AB1" s="26"/>
-      <c r="AC1" s="26"/>
-      <c r="AD1" s="26"/>
-      <c r="AE1" s="26"/>
-      <c r="AF1" s="26"/>
-      <c r="AG1" s="26"/>
-      <c r="AH1" s="26" t="s">
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="27"/>
+      <c r="AC1" s="27"/>
+      <c r="AD1" s="27"/>
+      <c r="AE1" s="27"/>
+      <c r="AF1" s="27"/>
+      <c r="AG1" s="27"/>
+      <c r="AH1" s="27" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
+      <c r="A2" s="27"/>
+      <c r="B2" s="27"/>
       <c r="C2" s="5">
         <v>1</v>
       </c>
@@ -4940,7 +5148,7 @@
       <c r="AG2" s="5">
         <v>31</v>
       </c>
-      <c r="AH2" s="26"/>
+      <c r="AH2" s="27"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
@@ -5805,16 +6013,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="23"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -5859,11 +6067,11 @@
       </c>
       <c r="E3" s="3">
         <f>SUM('Nhập xuất tồn'!E3)</f>
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F3" s="3">
         <f>SUM(C3+D3-E3)</f>
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G3" s="4">
         <f>'Nhập xuất tồn'!G3</f>
@@ -5871,7 +6079,7 @@
       </c>
       <c r="H3" s="3">
         <f>SUM(F3-G3)</f>
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -6332,10 +6540,10 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="34" t="s">
+      <c r="A19" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="34"/>
+      <c r="B19" s="35"/>
       <c r="C19" s="10">
         <f>SUM(C3:C17)</f>
         <v>134</v>
@@ -6346,11 +6554,11 @@
       </c>
       <c r="E19" s="10">
         <f>SUM(E3:E17)</f>
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
@@ -6358,7 +6566,7 @@
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21969420-82A6-4961-B6E7-5DF0DC9E9863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E02A2C4-C52F-493E-8F01-A166A316DAF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ghi chú'!$A$1:$F$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ghi chú'!$A$1:$F$54</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="95">
   <si>
     <t>VNSH01</t>
   </si>
@@ -318,6 +318,9 @@
   </si>
   <si>
     <t>GSATCOM</t>
+  </si>
+  <si>
+    <t>Đã trả (20/03/26)</t>
   </si>
 </sst>
 </file>
@@ -579,16 +582,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1085,22 +1088,22 @@
       </c>
       <c r="D3" s="3">
         <f>Nhập!AH3</f>
-        <v>65</v>
+        <v>142</v>
       </c>
       <c r="E3" s="3">
         <f>Xuất!AH4+Huỷ!AH3</f>
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F3" s="3">
         <f>C3+D3-E3</f>
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="G3" s="4">
         <v>2</v>
       </c>
       <c r="H3" s="3">
         <f>F3-G3</f>
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1719,15 +1722,15 @@
       </c>
       <c r="D24" s="3">
         <f t="shared" ref="D24:G24" si="2">SUM(D3:D22)</f>
-        <v>276</v>
+        <v>353</v>
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
@@ -1735,7 +1738,7 @@
       </c>
       <c r="H24" s="3">
         <f>SUM(H3:H23)</f>
-        <v>22</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1989,7 +1992,9 @@
       <c r="U4" s="5">
         <v>10</v>
       </c>
-      <c r="V4" s="5"/>
+      <c r="V4" s="5">
+        <v>8</v>
+      </c>
       <c r="W4" s="5">
         <v>9</v>
       </c>
@@ -2005,7 +2010,7 @@
       <c r="AG4" s="5"/>
       <c r="AH4" s="5">
         <f>SUM(C4:AG4)</f>
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
@@ -2102,7 +2107,7 @@
       <c r="AF6" s="5"/>
       <c r="AG6" s="5"/>
       <c r="AH6" s="5">
-        <f t="shared" ref="AH5:AH18" si="0">SUM(C6:AG6)</f>
+        <f t="shared" ref="AH6:AH18" si="0">SUM(C6:AG6)</f>
         <v>0</v>
       </c>
     </row>
@@ -3069,7 +3074,9 @@
       <c r="V3" s="5"/>
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
+      <c r="Y3" s="5">
+        <v>77</v>
+      </c>
       <c r="Z3" s="5"/>
       <c r="AA3" s="5"/>
       <c r="AB3" s="5"/>
@@ -3080,7 +3087,7 @@
       <c r="AG3" s="5"/>
       <c r="AH3" s="5">
         <f>SUM(C3:AG3)</f>
-        <v>65</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
@@ -3950,8 +3957,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7C51F44-131D-46D9-8F20-A11BD47AE60F}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="16" customWidth="1"/>
@@ -3987,8 +3993,8 @@
       </c>
       <c r="H1" s="12"/>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="34">
         <v>46055</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -4004,8 +4010,8 @@
       </c>
       <c r="G2" s="15"/>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="31"/>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="34"/>
       <c r="B3" s="15" t="s">
         <v>39</v>
       </c>
@@ -4019,8 +4025,8 @@
       </c>
       <c r="G3" s="15"/>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="34"/>
       <c r="B4" s="15" t="s">
         <v>40</v>
       </c>
@@ -4034,8 +4040,8 @@
       </c>
       <c r="G4" s="15"/>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31"/>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="34"/>
       <c r="B5" s="15" t="s">
         <v>41</v>
       </c>
@@ -4049,8 +4055,8 @@
       </c>
       <c r="G5" s="15"/>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="31">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="34">
         <v>46056</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -4066,8 +4072,8 @@
       </c>
       <c r="G6" s="15"/>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="31"/>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="34"/>
       <c r="B7" s="15" t="s">
         <v>43</v>
       </c>
@@ -4081,8 +4087,8 @@
       </c>
       <c r="G7" s="15"/>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="31">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="34">
         <v>46057</v>
       </c>
       <c r="B8" s="14" t="s">
@@ -4098,8 +4104,8 @@
       </c>
       <c r="G8" s="15"/>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="34"/>
       <c r="B9" s="15" t="s">
         <v>39</v>
       </c>
@@ -4113,8 +4119,8 @@
       </c>
       <c r="G9" s="15"/>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="31">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="34">
         <v>46058</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -4130,8 +4136,8 @@
       </c>
       <c r="G10" s="15"/>
     </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="34"/>
       <c r="B11" s="15" t="s">
         <v>49</v>
       </c>
@@ -4145,8 +4151,8 @@
       </c>
       <c r="G11" s="15"/>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="31">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="34">
         <v>46059</v>
       </c>
       <c r="B12" s="15" t="s">
@@ -4162,8 +4168,8 @@
       </c>
       <c r="G12" s="15"/>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="31"/>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="34"/>
       <c r="B13" s="15" t="s">
         <v>50</v>
       </c>
@@ -4177,7 +4183,7 @@
       </c>
       <c r="G13" s="15"/>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>46060</v>
       </c>
@@ -4194,8 +4200,8 @@
       </c>
       <c r="G14" s="15"/>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="31">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="34">
         <v>46062</v>
       </c>
       <c r="B15" s="15" t="s">
@@ -4211,8 +4217,8 @@
       </c>
       <c r="G15" s="15"/>
     </row>
-    <row r="16" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="31"/>
+    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="34"/>
       <c r="B16" s="15" t="s">
         <v>41</v>
       </c>
@@ -4226,7 +4232,7 @@
       </c>
       <c r="G16" s="15"/>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>46063</v>
       </c>
@@ -4243,7 +4249,7 @@
       </c>
       <c r="G17" s="15"/>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>46064</v>
       </c>
@@ -4260,8 +4266,8 @@
       </c>
       <c r="G18" s="15"/>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="31">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="34">
         <v>46065</v>
       </c>
       <c r="B19" s="15" t="s">
@@ -4277,8 +4283,8 @@
       </c>
       <c r="G19" s="15"/>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="31"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="34"/>
       <c r="B20" s="15" t="s">
         <v>49</v>
       </c>
@@ -4292,8 +4298,8 @@
       </c>
       <c r="G20" s="15"/>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="32">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="31">
         <v>46076</v>
       </c>
       <c r="B21" s="15" t="s">
@@ -4309,8 +4315,8 @@
       </c>
       <c r="G21" s="15"/>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="32"/>
       <c r="B22" s="15" t="s">
         <v>64</v>
       </c>
@@ -4324,7 +4330,7 @@
       </c>
       <c r="G22" s="15"/>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="33"/>
       <c r="B23" s="15" t="s">
         <v>66</v>
@@ -4339,8 +4345,8 @@
       </c>
       <c r="G23" s="15"/>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="32">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="31">
         <v>46077</v>
       </c>
       <c r="B24" s="15" t="s">
@@ -4356,8 +4362,8 @@
       </c>
       <c r="G24" s="15"/>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="34"/>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="32"/>
       <c r="B25" s="15" t="s">
         <v>63</v>
       </c>
@@ -4371,7 +4377,7 @@
       </c>
       <c r="G25" s="15"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="33"/>
       <c r="B26" s="15" t="s">
         <v>14</v>
@@ -4387,7 +4393,7 @@
       <c r="G26" s="15"/>
     </row>
     <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="32">
+      <c r="A27" s="31">
         <v>46078</v>
       </c>
       <c r="B27" s="15" t="s">
@@ -4407,7 +4413,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="33"/>
       <c r="B28" s="15" t="s">
         <v>49</v>
@@ -4422,8 +4428,8 @@
       </c>
       <c r="G28" s="15"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="32">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="31">
         <v>46079</v>
       </c>
       <c r="B29" s="15" t="s">
@@ -4441,8 +4447,8 @@
       </c>
       <c r="G29" s="15"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="34"/>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="32"/>
       <c r="B30" s="15" t="s">
         <v>69</v>
       </c>
@@ -4490,8 +4496,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="32">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="31">
         <v>46083</v>
       </c>
       <c r="B33" s="15" t="s">
@@ -4507,8 +4513,8 @@
       </c>
       <c r="G33" s="15"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="34"/>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="32"/>
       <c r="B34" s="15" t="s">
         <v>49</v>
       </c>
@@ -4522,8 +4528,8 @@
       </c>
       <c r="G34" s="15"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="34"/>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="32"/>
       <c r="B35" s="15" t="s">
         <v>14</v>
       </c>
@@ -4537,8 +4543,8 @@
       </c>
       <c r="G35" s="15"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="34"/>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="32"/>
       <c r="B36" s="15" t="s">
         <v>74</v>
       </c>
@@ -4554,8 +4560,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="34"/>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="32"/>
       <c r="B37" s="15" t="s">
         <v>75</v>
       </c>
@@ -4568,12 +4574,8 @@
         <v>76</v>
       </c>
       <c r="G37" s="15"/>
-      <c r="J37" s="13">
-        <f>SUM(E27:E51)</f>
-        <v>372</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="33"/>
       <c r="B38" s="15" t="s">
         <v>61</v>
@@ -4588,7 +4590,7 @@
       </c>
       <c r="G38" s="15"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="14">
         <v>46084</v>
       </c>
@@ -4605,8 +4607,8 @@
       </c>
       <c r="G39" s="15"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="32">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="31">
         <v>46085</v>
       </c>
       <c r="B40" s="15" t="s">
@@ -4622,7 +4624,7 @@
       </c>
       <c r="G40" s="15"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="33"/>
       <c r="B41" s="15" t="s">
         <v>80</v>
@@ -4637,7 +4639,7 @@
       </c>
       <c r="G41" s="15"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="14">
         <v>46086</v>
       </c>
@@ -4654,8 +4656,8 @@
       </c>
       <c r="G42" s="15"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="32">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="31">
         <v>46090</v>
       </c>
       <c r="B43" s="15" t="s">
@@ -4671,7 +4673,7 @@
       </c>
       <c r="G43" s="15"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="33"/>
       <c r="B44" s="15" t="s">
         <v>84</v>
@@ -4686,7 +4688,7 @@
       </c>
       <c r="G44" s="15"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="14">
         <v>46091</v>
       </c>
@@ -4703,7 +4705,7 @@
       </c>
       <c r="G45" s="15"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="14">
         <v>46092</v>
       </c>
@@ -4720,8 +4722,8 @@
       </c>
       <c r="G46" s="15"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="31">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="34">
         <v>46094</v>
       </c>
       <c r="B47" s="15" t="s">
@@ -4737,8 +4739,8 @@
       </c>
       <c r="G47" s="15"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="31"/>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="34"/>
       <c r="B48" s="15" t="s">
         <v>74</v>
       </c>
@@ -4769,63 +4771,63 @@
       </c>
       <c r="G49" s="15"/>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="32">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="14">
+        <v>46100</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15">
+        <v>8</v>
+      </c>
+      <c r="E50" s="15"/>
+      <c r="F50" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="G50" s="15"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="31">
         <v>46101</v>
       </c>
-      <c r="B50" s="15" t="s">
+      <c r="B51" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15">
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15">
         <v>20</v>
       </c>
-      <c r="F50" s="15" t="s">
+      <c r="F51" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="G50" s="21"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="34"/>
-      <c r="B51" s="15" t="s">
+      <c r="G51" s="21"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="32"/>
+      <c r="B52" s="15" t="s">
         <v>74</v>
-      </c>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15">
-        <v>9</v>
-      </c>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="G51" s="21"/>
-    </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="33"/>
-      <c r="B52" s="15" t="s">
-        <v>49</v>
       </c>
       <c r="C52" s="15"/>
       <c r="D52" s="15">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E52" s="15"/>
       <c r="F52" s="15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G52" s="21"/>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="15">
-        <v>21</v>
-      </c>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="33"/>
       <c r="B53" s="15" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="C53" s="15"/>
       <c r="D53" s="15">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="15" t="s">
@@ -4834,12 +4836,20 @@
       <c r="G53" s="21"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="15"/>
-      <c r="B54" s="15"/>
+      <c r="A54" s="14">
+        <v>46102</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>93</v>
+      </c>
       <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
+      <c r="D54" s="15">
+        <v>58</v>
+      </c>
       <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
+      <c r="F54" s="15" t="s">
+        <v>91</v>
+      </c>
       <c r="G54" s="21"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -4986,42 +4996,36 @@
       <c r="F70" s="15"/>
       <c r="G70" s="21"/>
     </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="15"/>
+      <c r="B71" s="15"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="15"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="15"/>
+      <c r="G71" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F53" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="Đã trả (02/03/26)"/>
-        <filter val="Đã trả (03/03/26)"/>
-        <filter val="Đã trả (04/03/26)"/>
-        <filter val="Đã trả (05/03/26)"/>
-        <filter val="Đã trả (07/03/26)"/>
-        <filter val="Đã trả (09/03/26)"/>
-        <filter val="Đã trả (11/03/26)"/>
-        <filter val="Đã trả (13/03/26)"/>
-        <filter val="Đã trả (19/03/26)"/>
-        <filter val="Đã trả (21/03/26)"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:F54" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
   <mergeCells count="16">
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="A33:A38"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A29:A31"/>
   </mergeCells>
-  <conditionalFormatting sqref="D2:F1000">
+  <conditionalFormatting sqref="D2:F1001">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>ISNUMBER(SEARCH("Đã trả",$F2))</formula>
     </cfRule>
@@ -6099,15 +6103,15 @@
       </c>
       <c r="D3" s="3">
         <f>SUM('Nhập xuất tồn'!D3)</f>
-        <v>65</v>
+        <v>142</v>
       </c>
       <c r="E3" s="3">
         <f>SUM('Nhập xuất tồn'!E3)</f>
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F3" s="3">
         <f>SUM(C3+D3-E3)</f>
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="G3" s="4">
         <f>'Nhập xuất tồn'!G3</f>
@@ -6115,7 +6119,7 @@
       </c>
       <c r="H3" s="3">
         <f>SUM(F3-G3)</f>
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -6586,15 +6590,15 @@
       </c>
       <c r="D19" s="10">
         <f>SUM(D3:D17)</f>
-        <v>276</v>
+        <v>353</v>
       </c>
       <c r="E19" s="10">
         <f>SUM(E3:E17)</f>
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
@@ -6602,7 +6606,7 @@
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>49</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E02A2C4-C52F-493E-8F01-A166A316DAF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{047399A1-D306-446F-ACFC-482724E4EE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
@@ -35,6 +35,40 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>TungNM</author>
+  </authors>
+  <commentList>
+    <comment ref="Y5" authorId="0" shapeId="0" xr:uid="{1E560BF5-5B73-4A43-81C3-C897C7151622}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>TungNM:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+trả lại kho</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="95">
   <si>
@@ -327,7 +361,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -367,6 +401,19 @@
       <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -582,16 +629,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1123,11 +1170,11 @@
       </c>
       <c r="E4" s="3">
         <f>Xuất!AH5+Huỷ!AH4</f>
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F4" s="3">
         <f>C4+D4-E4</f>
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="3"/>
@@ -1726,11 +1773,11 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
@@ -1770,7 +1817,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AH24"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2054,7 +2101,9 @@
       <c r="V5" s="5"/>
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
-      <c r="Y5" s="5"/>
+      <c r="Y5" s="5">
+        <v>5</v>
+      </c>
       <c r="Z5" s="5"/>
       <c r="AA5" s="5"/>
       <c r="AB5" s="5"/>
@@ -2065,7 +2114,7 @@
       <c r="AG5" s="5"/>
       <c r="AH5" s="5">
         <f>SUM(C5:AG5)</f>
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
@@ -2881,6 +2930,7 @@
     <mergeCell ref="AH2:AH3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3994,7 +4044,7 @@
       <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="34">
+      <c r="A2" s="31">
         <v>46055</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -4011,7 +4061,7 @@
       <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="34"/>
+      <c r="A3" s="31"/>
       <c r="B3" s="15" t="s">
         <v>39</v>
       </c>
@@ -4026,7 +4076,7 @@
       <c r="G3" s="15"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="34"/>
+      <c r="A4" s="31"/>
       <c r="B4" s="15" t="s">
         <v>40</v>
       </c>
@@ -4041,7 +4091,7 @@
       <c r="G4" s="15"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="34"/>
+      <c r="A5" s="31"/>
       <c r="B5" s="15" t="s">
         <v>41</v>
       </c>
@@ -4056,7 +4106,7 @@
       <c r="G5" s="15"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="34">
+      <c r="A6" s="31">
         <v>46056</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -4073,7 +4123,7 @@
       <c r="G6" s="15"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="34"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="15" t="s">
         <v>43</v>
       </c>
@@ -4088,7 +4138,7 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="34">
+      <c r="A8" s="31">
         <v>46057</v>
       </c>
       <c r="B8" s="14" t="s">
@@ -4105,7 +4155,7 @@
       <c r="G8" s="15"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="34"/>
+      <c r="A9" s="31"/>
       <c r="B9" s="15" t="s">
         <v>39</v>
       </c>
@@ -4120,7 +4170,7 @@
       <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="34">
+      <c r="A10" s="31">
         <v>46058</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -4137,7 +4187,7 @@
       <c r="G10" s="15"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="34"/>
+      <c r="A11" s="31"/>
       <c r="B11" s="15" t="s">
         <v>49</v>
       </c>
@@ -4152,7 +4202,7 @@
       <c r="G11" s="15"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="34">
+      <c r="A12" s="31">
         <v>46059</v>
       </c>
       <c r="B12" s="15" t="s">
@@ -4169,7 +4219,7 @@
       <c r="G12" s="15"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="34"/>
+      <c r="A13" s="31"/>
       <c r="B13" s="15" t="s">
         <v>50</v>
       </c>
@@ -4201,7 +4251,7 @@
       <c r="G14" s="15"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="34">
+      <c r="A15" s="31">
         <v>46062</v>
       </c>
       <c r="B15" s="15" t="s">
@@ -4218,7 +4268,7 @@
       <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="34"/>
+      <c r="A16" s="31"/>
       <c r="B16" s="15" t="s">
         <v>41</v>
       </c>
@@ -4267,7 +4317,7 @@
       <c r="G18" s="15"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="34">
+      <c r="A19" s="31">
         <v>46065</v>
       </c>
       <c r="B19" s="15" t="s">
@@ -4284,7 +4334,7 @@
       <c r="G19" s="15"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="34"/>
+      <c r="A20" s="31"/>
       <c r="B20" s="15" t="s">
         <v>49</v>
       </c>
@@ -4299,7 +4349,7 @@
       <c r="G20" s="15"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="31">
+      <c r="A21" s="32">
         <v>46076</v>
       </c>
       <c r="B21" s="15" t="s">
@@ -4316,7 +4366,7 @@
       <c r="G21" s="15"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="32"/>
+      <c r="A22" s="34"/>
       <c r="B22" s="15" t="s">
         <v>64</v>
       </c>
@@ -4346,7 +4396,7 @@
       <c r="G23" s="15"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="31">
+      <c r="A24" s="32">
         <v>46077</v>
       </c>
       <c r="B24" s="15" t="s">
@@ -4363,7 +4413,7 @@
       <c r="G24" s="15"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="32"/>
+      <c r="A25" s="34"/>
       <c r="B25" s="15" t="s">
         <v>63</v>
       </c>
@@ -4393,7 +4443,7 @@
       <c r="G26" s="15"/>
     </row>
     <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="31">
+      <c r="A27" s="32">
         <v>46078</v>
       </c>
       <c r="B27" s="15" t="s">
@@ -4429,7 +4479,7 @@
       <c r="G28" s="15"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="31">
+      <c r="A29" s="32">
         <v>46079</v>
       </c>
       <c r="B29" s="15" t="s">
@@ -4448,7 +4498,7 @@
       <c r="G29" s="15"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="32"/>
+      <c r="A30" s="34"/>
       <c r="B30" s="15" t="s">
         <v>69</v>
       </c>
@@ -4497,7 +4547,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="31">
+      <c r="A33" s="32">
         <v>46083</v>
       </c>
       <c r="B33" s="15" t="s">
@@ -4514,7 +4564,7 @@
       <c r="G33" s="15"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="32"/>
+      <c r="A34" s="34"/>
       <c r="B34" s="15" t="s">
         <v>49</v>
       </c>
@@ -4529,7 +4579,7 @@
       <c r="G34" s="15"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="32"/>
+      <c r="A35" s="34"/>
       <c r="B35" s="15" t="s">
         <v>14</v>
       </c>
@@ -4544,7 +4594,7 @@
       <c r="G35" s="15"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="32"/>
+      <c r="A36" s="34"/>
       <c r="B36" s="15" t="s">
         <v>74</v>
       </c>
@@ -4561,7 +4611,7 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="32"/>
+      <c r="A37" s="34"/>
       <c r="B37" s="15" t="s">
         <v>75</v>
       </c>
@@ -4608,7 +4658,7 @@
       <c r="G39" s="15"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="31">
+      <c r="A40" s="32">
         <v>46085</v>
       </c>
       <c r="B40" s="15" t="s">
@@ -4657,7 +4707,7 @@
       <c r="G42" s="15"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="31">
+      <c r="A43" s="32">
         <v>46090</v>
       </c>
       <c r="B43" s="15" t="s">
@@ -4723,7 +4773,7 @@
       <c r="G46" s="15"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="34">
+      <c r="A47" s="31">
         <v>46094</v>
       </c>
       <c r="B47" s="15" t="s">
@@ -4740,7 +4790,7 @@
       <c r="G47" s="15"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="34"/>
+      <c r="A48" s="31"/>
       <c r="B48" s="15" t="s">
         <v>74</v>
       </c>
@@ -4789,7 +4839,7 @@
       <c r="G50" s="15"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="31">
+      <c r="A51" s="32">
         <v>46101</v>
       </c>
       <c r="B51" s="15" t="s">
@@ -4806,7 +4856,7 @@
       <c r="G51" s="21"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="32"/>
+      <c r="A52" s="34"/>
       <c r="B52" s="15" t="s">
         <v>74</v>
       </c>
@@ -5008,22 +5058,22 @@
   </sheetData>
   <autoFilter ref="A1:F54" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
   <mergeCells count="16">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A29:A31"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="A33:A38"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:F1001">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -6139,11 +6189,11 @@
       </c>
       <c r="E4" s="3">
         <f>SUM('Nhập xuất tồn'!E4)</f>
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F4" s="3">
         <f>SUM(C4+D4-E4)</f>
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G4" s="4">
         <f>'Nhập xuất tồn'!G4</f>
@@ -6151,7 +6201,7 @@
       </c>
       <c r="H4" s="3">
         <f>SUM(F4-G4)</f>
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -6594,11 +6644,11 @@
       </c>
       <c r="E19" s="10">
         <f>SUM(E3:E17)</f>
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
@@ -6606,7 +6656,7 @@
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{047399A1-D306-446F-ACFC-482724E4EE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{742AC8CC-3A51-440A-9C11-47D6C7AF6CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="96">
   <si>
     <t>VNSH01</t>
   </si>
@@ -355,6 +355,9 @@
   </si>
   <si>
     <t>Đã trả (20/03/26)</t>
+  </si>
+  <si>
+    <t>Đã trả (24/03/26)</t>
   </si>
 </sst>
 </file>
@@ -629,16 +632,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1139,18 +1142,18 @@
       </c>
       <c r="E3" s="3">
         <f>Xuất!AH4+Huỷ!AH3</f>
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="F3" s="3">
         <f>C3+D3-E3</f>
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="G3" s="4">
         <v>2</v>
       </c>
       <c r="H3" s="3">
         <f>F3-G3</f>
-        <v>81</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1170,11 +1173,11 @@
       </c>
       <c r="E4" s="3">
         <f>Xuất!AH5+Huỷ!AH4</f>
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="F4" s="3">
         <f>C4+D4-E4</f>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="3"/>
@@ -1773,11 +1776,11 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
-        <v>372</v>
+        <v>418</v>
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
@@ -1785,7 +1788,7 @@
       </c>
       <c r="H24" s="3">
         <f>SUM(H3:H23)</f>
-        <v>91</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -2047,7 +2050,9 @@
       </c>
       <c r="X4" s="5"/>
       <c r="Y4" s="5"/>
-      <c r="Z4" s="5"/>
+      <c r="Z4" s="5">
+        <v>25</v>
+      </c>
       <c r="AA4" s="5"/>
       <c r="AB4" s="5"/>
       <c r="AC4" s="5"/>
@@ -2057,7 +2062,7 @@
       <c r="AG4" s="5"/>
       <c r="AH4" s="5">
         <f>SUM(C4:AG4)</f>
-        <v>61</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
@@ -2104,7 +2109,9 @@
       <c r="Y5" s="5">
         <v>5</v>
       </c>
-      <c r="Z5" s="5"/>
+      <c r="Z5" s="5">
+        <v>21</v>
+      </c>
       <c r="AA5" s="5"/>
       <c r="AB5" s="5"/>
       <c r="AC5" s="5"/>
@@ -2114,7 +2121,7 @@
       <c r="AG5" s="5"/>
       <c r="AH5" s="5">
         <f>SUM(C5:AG5)</f>
-        <v>311</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
@@ -4044,7 +4051,7 @@
       <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="31">
+      <c r="A2" s="34">
         <v>46055</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -4061,7 +4068,7 @@
       <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="31"/>
+      <c r="A3" s="34"/>
       <c r="B3" s="15" t="s">
         <v>39</v>
       </c>
@@ -4076,7 +4083,7 @@
       <c r="G3" s="15"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
+      <c r="A4" s="34"/>
       <c r="B4" s="15" t="s">
         <v>40</v>
       </c>
@@ -4091,7 +4098,7 @@
       <c r="G4" s="15"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="31"/>
+      <c r="A5" s="34"/>
       <c r="B5" s="15" t="s">
         <v>41</v>
       </c>
@@ -4106,7 +4113,7 @@
       <c r="G5" s="15"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="31">
+      <c r="A6" s="34">
         <v>46056</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -4123,7 +4130,7 @@
       <c r="G6" s="15"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="31"/>
+      <c r="A7" s="34"/>
       <c r="B7" s="15" t="s">
         <v>43</v>
       </c>
@@ -4138,7 +4145,7 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="31">
+      <c r="A8" s="34">
         <v>46057</v>
       </c>
       <c r="B8" s="14" t="s">
@@ -4155,7 +4162,7 @@
       <c r="G8" s="15"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
+      <c r="A9" s="34"/>
       <c r="B9" s="15" t="s">
         <v>39</v>
       </c>
@@ -4170,7 +4177,7 @@
       <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="31">
+      <c r="A10" s="34">
         <v>46058</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -4187,7 +4194,7 @@
       <c r="G10" s="15"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
+      <c r="A11" s="34"/>
       <c r="B11" s="15" t="s">
         <v>49</v>
       </c>
@@ -4202,7 +4209,7 @@
       <c r="G11" s="15"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="31">
+      <c r="A12" s="34">
         <v>46059</v>
       </c>
       <c r="B12" s="15" t="s">
@@ -4219,7 +4226,7 @@
       <c r="G12" s="15"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="31"/>
+      <c r="A13" s="34"/>
       <c r="B13" s="15" t="s">
         <v>50</v>
       </c>
@@ -4251,7 +4258,7 @@
       <c r="G14" s="15"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="31">
+      <c r="A15" s="34">
         <v>46062</v>
       </c>
       <c r="B15" s="15" t="s">
@@ -4268,7 +4275,7 @@
       <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="31"/>
+      <c r="A16" s="34"/>
       <c r="B16" s="15" t="s">
         <v>41</v>
       </c>
@@ -4317,7 +4324,7 @@
       <c r="G18" s="15"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="31">
+      <c r="A19" s="34">
         <v>46065</v>
       </c>
       <c r="B19" s="15" t="s">
@@ -4334,7 +4341,7 @@
       <c r="G19" s="15"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="31"/>
+      <c r="A20" s="34"/>
       <c r="B20" s="15" t="s">
         <v>49</v>
       </c>
@@ -4349,7 +4356,7 @@
       <c r="G20" s="15"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="32">
+      <c r="A21" s="31">
         <v>46076</v>
       </c>
       <c r="B21" s="15" t="s">
@@ -4366,7 +4373,7 @@
       <c r="G21" s="15"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
+      <c r="A22" s="32"/>
       <c r="B22" s="15" t="s">
         <v>64</v>
       </c>
@@ -4396,7 +4403,7 @@
       <c r="G23" s="15"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="32">
+      <c r="A24" s="31">
         <v>46077</v>
       </c>
       <c r="B24" s="15" t="s">
@@ -4413,7 +4420,7 @@
       <c r="G24" s="15"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="34"/>
+      <c r="A25" s="32"/>
       <c r="B25" s="15" t="s">
         <v>63</v>
       </c>
@@ -4443,7 +4450,7 @@
       <c r="G26" s="15"/>
     </row>
     <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="32">
+      <c r="A27" s="31">
         <v>46078</v>
       </c>
       <c r="B27" s="15" t="s">
@@ -4479,7 +4486,7 @@
       <c r="G28" s="15"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="32">
+      <c r="A29" s="31">
         <v>46079</v>
       </c>
       <c r="B29" s="15" t="s">
@@ -4498,7 +4505,7 @@
       <c r="G29" s="15"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="34"/>
+      <c r="A30" s="32"/>
       <c r="B30" s="15" t="s">
         <v>69</v>
       </c>
@@ -4547,7 +4554,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="32">
+      <c r="A33" s="31">
         <v>46083</v>
       </c>
       <c r="B33" s="15" t="s">
@@ -4564,7 +4571,7 @@
       <c r="G33" s="15"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="34"/>
+      <c r="A34" s="32"/>
       <c r="B34" s="15" t="s">
         <v>49</v>
       </c>
@@ -4579,7 +4586,7 @@
       <c r="G34" s="15"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="34"/>
+      <c r="A35" s="32"/>
       <c r="B35" s="15" t="s">
         <v>14</v>
       </c>
@@ -4594,7 +4601,7 @@
       <c r="G35" s="15"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="34"/>
+      <c r="A36" s="32"/>
       <c r="B36" s="15" t="s">
         <v>74</v>
       </c>
@@ -4611,7 +4618,7 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="34"/>
+      <c r="A37" s="32"/>
       <c r="B37" s="15" t="s">
         <v>75</v>
       </c>
@@ -4658,7 +4665,7 @@
       <c r="G39" s="15"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="32">
+      <c r="A40" s="31">
         <v>46085</v>
       </c>
       <c r="B40" s="15" t="s">
@@ -4707,7 +4714,7 @@
       <c r="G42" s="15"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="32">
+      <c r="A43" s="31">
         <v>46090</v>
       </c>
       <c r="B43" s="15" t="s">
@@ -4773,7 +4780,7 @@
       <c r="G46" s="15"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="31">
+      <c r="A47" s="34">
         <v>46094</v>
       </c>
       <c r="B47" s="15" t="s">
@@ -4790,7 +4797,7 @@
       <c r="G47" s="15"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="31"/>
+      <c r="A48" s="34"/>
       <c r="B48" s="15" t="s">
         <v>74</v>
       </c>
@@ -4839,7 +4846,7 @@
       <c r="G50" s="15"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="32">
+      <c r="A51" s="31">
         <v>46101</v>
       </c>
       <c r="B51" s="15" t="s">
@@ -4851,12 +4858,12 @@
         <v>20</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G51" s="21"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="34"/>
+      <c r="A52" s="32"/>
       <c r="B52" s="15" t="s">
         <v>74</v>
       </c>
@@ -4881,7 +4888,7 @@
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="15" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G53" s="21"/>
     </row>
@@ -4903,12 +4910,20 @@
       <c r="G54" s="21"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="15"/>
-      <c r="B55" s="15"/>
+      <c r="A55" s="14">
+        <v>46105</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>83</v>
+      </c>
       <c r="C55" s="15"/>
       <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
+      <c r="E55" s="15">
+        <v>1</v>
+      </c>
+      <c r="F55" s="15" t="s">
+        <v>95</v>
+      </c>
       <c r="G55" s="21"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -5058,22 +5073,22 @@
   </sheetData>
   <autoFilter ref="A1:F54" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
   <mergeCells count="16">
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="A33:A38"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A29:A31"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:F1001">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -6157,11 +6172,11 @@
       </c>
       <c r="E3" s="3">
         <f>SUM('Nhập xuất tồn'!E3)</f>
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="F3" s="3">
         <f>SUM(C3+D3-E3)</f>
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="G3" s="4">
         <f>'Nhập xuất tồn'!G3</f>
@@ -6169,7 +6184,7 @@
       </c>
       <c r="H3" s="3">
         <f>SUM(F3-G3)</f>
-        <v>81</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -6189,11 +6204,11 @@
       </c>
       <c r="E4" s="3">
         <f>SUM('Nhập xuất tồn'!E4)</f>
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="F4" s="3">
         <f>SUM(C4+D4-E4)</f>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G4" s="4">
         <f>'Nhập xuất tồn'!G4</f>
@@ -6201,7 +6216,7 @@
       </c>
       <c r="H4" s="3">
         <f>SUM(F4-G4)</f>
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -6644,11 +6659,11 @@
       </c>
       <c r="E19" s="10">
         <f>SUM(E3:E17)</f>
-        <v>372</v>
+        <v>418</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
@@ -6656,7 +6671,7 @@
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>113</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{742AC8CC-3A51-440A-9C11-47D6C7AF6CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E096E1F6-D298-454E-8786-CCCE1CC48EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
@@ -632,16 +632,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="D3" s="3">
         <f>Nhập!AH3</f>
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E3" s="3">
         <f>Xuất!AH4+Huỷ!AH3</f>
@@ -1146,14 +1146,14 @@
       </c>
       <c r="F3" s="3">
         <f>C3+D3-E3</f>
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G3" s="4">
         <v>2</v>
       </c>
       <c r="H3" s="3">
         <f>F3-G3</f>
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="D24" s="3">
         <f t="shared" ref="D24:G24" si="2">SUM(D3:D22)</f>
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="H24" s="3">
         <f>SUM(H3:H23)</f>
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -3135,7 +3135,9 @@
         <v>77</v>
       </c>
       <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
+      <c r="AA3" s="5">
+        <v>5</v>
+      </c>
       <c r="AB3" s="5"/>
       <c r="AC3" s="5"/>
       <c r="AD3" s="5"/>
@@ -3144,7 +3146,7 @@
       <c r="AG3" s="5"/>
       <c r="AH3" s="5">
         <f>SUM(C3:AG3)</f>
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
@@ -4051,7 +4053,7 @@
       <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="34">
+      <c r="A2" s="31">
         <v>46055</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -4068,7 +4070,7 @@
       <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="34"/>
+      <c r="A3" s="31"/>
       <c r="B3" s="15" t="s">
         <v>39</v>
       </c>
@@ -4083,7 +4085,7 @@
       <c r="G3" s="15"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="34"/>
+      <c r="A4" s="31"/>
       <c r="B4" s="15" t="s">
         <v>40</v>
       </c>
@@ -4098,7 +4100,7 @@
       <c r="G4" s="15"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="34"/>
+      <c r="A5" s="31"/>
       <c r="B5" s="15" t="s">
         <v>41</v>
       </c>
@@ -4113,7 +4115,7 @@
       <c r="G5" s="15"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="34">
+      <c r="A6" s="31">
         <v>46056</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -4130,7 +4132,7 @@
       <c r="G6" s="15"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="34"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="15" t="s">
         <v>43</v>
       </c>
@@ -4145,7 +4147,7 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="34">
+      <c r="A8" s="31">
         <v>46057</v>
       </c>
       <c r="B8" s="14" t="s">
@@ -4162,7 +4164,7 @@
       <c r="G8" s="15"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="34"/>
+      <c r="A9" s="31"/>
       <c r="B9" s="15" t="s">
         <v>39</v>
       </c>
@@ -4177,7 +4179,7 @@
       <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="34">
+      <c r="A10" s="31">
         <v>46058</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -4194,7 +4196,7 @@
       <c r="G10" s="15"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="34"/>
+      <c r="A11" s="31"/>
       <c r="B11" s="15" t="s">
         <v>49</v>
       </c>
@@ -4209,7 +4211,7 @@
       <c r="G11" s="15"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="34">
+      <c r="A12" s="31">
         <v>46059</v>
       </c>
       <c r="B12" s="15" t="s">
@@ -4226,7 +4228,7 @@
       <c r="G12" s="15"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="34"/>
+      <c r="A13" s="31"/>
       <c r="B13" s="15" t="s">
         <v>50</v>
       </c>
@@ -4258,7 +4260,7 @@
       <c r="G14" s="15"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="34">
+      <c r="A15" s="31">
         <v>46062</v>
       </c>
       <c r="B15" s="15" t="s">
@@ -4275,7 +4277,7 @@
       <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="34"/>
+      <c r="A16" s="31"/>
       <c r="B16" s="15" t="s">
         <v>41</v>
       </c>
@@ -4324,7 +4326,7 @@
       <c r="G18" s="15"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="34">
+      <c r="A19" s="31">
         <v>46065</v>
       </c>
       <c r="B19" s="15" t="s">
@@ -4341,7 +4343,7 @@
       <c r="G19" s="15"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="34"/>
+      <c r="A20" s="31"/>
       <c r="B20" s="15" t="s">
         <v>49</v>
       </c>
@@ -4356,7 +4358,7 @@
       <c r="G20" s="15"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="31">
+      <c r="A21" s="32">
         <v>46076</v>
       </c>
       <c r="B21" s="15" t="s">
@@ -4373,7 +4375,7 @@
       <c r="G21" s="15"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="32"/>
+      <c r="A22" s="34"/>
       <c r="B22" s="15" t="s">
         <v>64</v>
       </c>
@@ -4403,7 +4405,7 @@
       <c r="G23" s="15"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="31">
+      <c r="A24" s="32">
         <v>46077</v>
       </c>
       <c r="B24" s="15" t="s">
@@ -4420,7 +4422,7 @@
       <c r="G24" s="15"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="32"/>
+      <c r="A25" s="34"/>
       <c r="B25" s="15" t="s">
         <v>63</v>
       </c>
@@ -4450,7 +4452,7 @@
       <c r="G26" s="15"/>
     </row>
     <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="31">
+      <c r="A27" s="32">
         <v>46078</v>
       </c>
       <c r="B27" s="15" t="s">
@@ -4486,7 +4488,7 @@
       <c r="G28" s="15"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="31">
+      <c r="A29" s="32">
         <v>46079</v>
       </c>
       <c r="B29" s="15" t="s">
@@ -4505,7 +4507,7 @@
       <c r="G29" s="15"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="32"/>
+      <c r="A30" s="34"/>
       <c r="B30" s="15" t="s">
         <v>69</v>
       </c>
@@ -4554,7 +4556,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="31">
+      <c r="A33" s="32">
         <v>46083</v>
       </c>
       <c r="B33" s="15" t="s">
@@ -4571,7 +4573,7 @@
       <c r="G33" s="15"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="32"/>
+      <c r="A34" s="34"/>
       <c r="B34" s="15" t="s">
         <v>49</v>
       </c>
@@ -4586,7 +4588,7 @@
       <c r="G34" s="15"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="32"/>
+      <c r="A35" s="34"/>
       <c r="B35" s="15" t="s">
         <v>14</v>
       </c>
@@ -4601,7 +4603,7 @@
       <c r="G35" s="15"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="32"/>
+      <c r="A36" s="34"/>
       <c r="B36" s="15" t="s">
         <v>74</v>
       </c>
@@ -4618,7 +4620,7 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="32"/>
+      <c r="A37" s="34"/>
       <c r="B37" s="15" t="s">
         <v>75</v>
       </c>
@@ -4665,7 +4667,7 @@
       <c r="G39" s="15"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="31">
+      <c r="A40" s="32">
         <v>46085</v>
       </c>
       <c r="B40" s="15" t="s">
@@ -4714,7 +4716,7 @@
       <c r="G42" s="15"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="31">
+      <c r="A43" s="32">
         <v>46090</v>
       </c>
       <c r="B43" s="15" t="s">
@@ -4780,7 +4782,7 @@
       <c r="G46" s="15"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="34">
+      <c r="A47" s="31">
         <v>46094</v>
       </c>
       <c r="B47" s="15" t="s">
@@ -4797,7 +4799,7 @@
       <c r="G47" s="15"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="34"/>
+      <c r="A48" s="31"/>
       <c r="B48" s="15" t="s">
         <v>74</v>
       </c>
@@ -4846,7 +4848,7 @@
       <c r="G50" s="15"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="31">
+      <c r="A51" s="32">
         <v>46101</v>
       </c>
       <c r="B51" s="15" t="s">
@@ -4863,7 +4865,7 @@
       <c r="G51" s="21"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="32"/>
+      <c r="A52" s="34"/>
       <c r="B52" s="15" t="s">
         <v>74</v>
       </c>
@@ -5073,22 +5075,22 @@
   </sheetData>
   <autoFilter ref="A1:F54" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
   <mergeCells count="16">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A29:A31"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="A33:A38"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:F1001">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -6168,7 +6170,7 @@
       </c>
       <c r="D3" s="3">
         <f>SUM('Nhập xuất tồn'!D3)</f>
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E3" s="3">
         <f>SUM('Nhập xuất tồn'!E3)</f>
@@ -6176,7 +6178,7 @@
       </c>
       <c r="F3" s="3">
         <f>SUM(C3+D3-E3)</f>
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G3" s="4">
         <f>'Nhập xuất tồn'!G3</f>
@@ -6184,7 +6186,7 @@
       </c>
       <c r="H3" s="3">
         <f>SUM(F3-G3)</f>
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -6655,7 +6657,7 @@
       </c>
       <c r="D19" s="10">
         <f>SUM(D3:D17)</f>
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="E19" s="10">
         <f>SUM(E3:E17)</f>
@@ -6663,7 +6665,7 @@
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
@@ -6671,7 +6673,7 @@
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E096E1F6-D298-454E-8786-CCCE1CC48EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B5A0E09-71A6-44B3-A6FE-7DF0C8AC564C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
@@ -632,16 +632,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="D3" s="3">
         <f>Nhập!AH3</f>
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E3" s="3">
         <f>Xuất!AH4+Huỷ!AH3</f>
@@ -1146,14 +1146,14 @@
       </c>
       <c r="F3" s="3">
         <f>C3+D3-E3</f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G3" s="4">
         <v>2</v>
       </c>
       <c r="H3" s="3">
         <f>F3-G3</f>
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="D24" s="3">
         <f t="shared" ref="D24:G24" si="2">SUM(D3:D22)</f>
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="H24" s="3">
         <f>SUM(H3:H23)</f>
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -3139,14 +3139,16 @@
         <v>5</v>
       </c>
       <c r="AB3" s="5"/>
-      <c r="AC3" s="5"/>
+      <c r="AC3" s="5">
+        <v>5</v>
+      </c>
       <c r="AD3" s="5"/>
       <c r="AE3" s="5"/>
       <c r="AF3" s="5"/>
       <c r="AG3" s="5"/>
       <c r="AH3" s="5">
         <f>SUM(C3:AG3)</f>
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
@@ -4053,7 +4055,7 @@
       <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="31">
+      <c r="A2" s="34">
         <v>46055</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -4070,7 +4072,7 @@
       <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="31"/>
+      <c r="A3" s="34"/>
       <c r="B3" s="15" t="s">
         <v>39</v>
       </c>
@@ -4085,7 +4087,7 @@
       <c r="G3" s="15"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
+      <c r="A4" s="34"/>
       <c r="B4" s="15" t="s">
         <v>40</v>
       </c>
@@ -4100,7 +4102,7 @@
       <c r="G4" s="15"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="31"/>
+      <c r="A5" s="34"/>
       <c r="B5" s="15" t="s">
         <v>41</v>
       </c>
@@ -4115,7 +4117,7 @@
       <c r="G5" s="15"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="31">
+      <c r="A6" s="34">
         <v>46056</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -4132,7 +4134,7 @@
       <c r="G6" s="15"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="31"/>
+      <c r="A7" s="34"/>
       <c r="B7" s="15" t="s">
         <v>43</v>
       </c>
@@ -4147,7 +4149,7 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="31">
+      <c r="A8" s="34">
         <v>46057</v>
       </c>
       <c r="B8" s="14" t="s">
@@ -4164,7 +4166,7 @@
       <c r="G8" s="15"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
+      <c r="A9" s="34"/>
       <c r="B9" s="15" t="s">
         <v>39</v>
       </c>
@@ -4179,7 +4181,7 @@
       <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="31">
+      <c r="A10" s="34">
         <v>46058</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -4196,7 +4198,7 @@
       <c r="G10" s="15"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
+      <c r="A11" s="34"/>
       <c r="B11" s="15" t="s">
         <v>49</v>
       </c>
@@ -4211,7 +4213,7 @@
       <c r="G11" s="15"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="31">
+      <c r="A12" s="34">
         <v>46059</v>
       </c>
       <c r="B12" s="15" t="s">
@@ -4228,7 +4230,7 @@
       <c r="G12" s="15"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="31"/>
+      <c r="A13" s="34"/>
       <c r="B13" s="15" t="s">
         <v>50</v>
       </c>
@@ -4260,7 +4262,7 @@
       <c r="G14" s="15"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="31">
+      <c r="A15" s="34">
         <v>46062</v>
       </c>
       <c r="B15" s="15" t="s">
@@ -4277,7 +4279,7 @@
       <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="31"/>
+      <c r="A16" s="34"/>
       <c r="B16" s="15" t="s">
         <v>41</v>
       </c>
@@ -4326,7 +4328,7 @@
       <c r="G18" s="15"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="31">
+      <c r="A19" s="34">
         <v>46065</v>
       </c>
       <c r="B19" s="15" t="s">
@@ -4343,7 +4345,7 @@
       <c r="G19" s="15"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="31"/>
+      <c r="A20" s="34"/>
       <c r="B20" s="15" t="s">
         <v>49</v>
       </c>
@@ -4358,7 +4360,7 @@
       <c r="G20" s="15"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="32">
+      <c r="A21" s="31">
         <v>46076</v>
       </c>
       <c r="B21" s="15" t="s">
@@ -4375,7 +4377,7 @@
       <c r="G21" s="15"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
+      <c r="A22" s="32"/>
       <c r="B22" s="15" t="s">
         <v>64</v>
       </c>
@@ -4405,7 +4407,7 @@
       <c r="G23" s="15"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="32">
+      <c r="A24" s="31">
         <v>46077</v>
       </c>
       <c r="B24" s="15" t="s">
@@ -4422,7 +4424,7 @@
       <c r="G24" s="15"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="34"/>
+      <c r="A25" s="32"/>
       <c r="B25" s="15" t="s">
         <v>63</v>
       </c>
@@ -4452,7 +4454,7 @@
       <c r="G26" s="15"/>
     </row>
     <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="32">
+      <c r="A27" s="31">
         <v>46078</v>
       </c>
       <c r="B27" s="15" t="s">
@@ -4488,7 +4490,7 @@
       <c r="G28" s="15"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="32">
+      <c r="A29" s="31">
         <v>46079</v>
       </c>
       <c r="B29" s="15" t="s">
@@ -4507,7 +4509,7 @@
       <c r="G29" s="15"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="34"/>
+      <c r="A30" s="32"/>
       <c r="B30" s="15" t="s">
         <v>69</v>
       </c>
@@ -4556,7 +4558,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="32">
+      <c r="A33" s="31">
         <v>46083</v>
       </c>
       <c r="B33" s="15" t="s">
@@ -4573,7 +4575,7 @@
       <c r="G33" s="15"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="34"/>
+      <c r="A34" s="32"/>
       <c r="B34" s="15" t="s">
         <v>49</v>
       </c>
@@ -4588,7 +4590,7 @@
       <c r="G34" s="15"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="34"/>
+      <c r="A35" s="32"/>
       <c r="B35" s="15" t="s">
         <v>14</v>
       </c>
@@ -4603,7 +4605,7 @@
       <c r="G35" s="15"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="34"/>
+      <c r="A36" s="32"/>
       <c r="B36" s="15" t="s">
         <v>74</v>
       </c>
@@ -4620,7 +4622,7 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="34"/>
+      <c r="A37" s="32"/>
       <c r="B37" s="15" t="s">
         <v>75</v>
       </c>
@@ -4667,7 +4669,7 @@
       <c r="G39" s="15"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="32">
+      <c r="A40" s="31">
         <v>46085</v>
       </c>
       <c r="B40" s="15" t="s">
@@ -4716,7 +4718,7 @@
       <c r="G42" s="15"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="32">
+      <c r="A43" s="31">
         <v>46090</v>
       </c>
       <c r="B43" s="15" t="s">
@@ -4782,7 +4784,7 @@
       <c r="G46" s="15"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="31">
+      <c r="A47" s="34">
         <v>46094</v>
       </c>
       <c r="B47" s="15" t="s">
@@ -4799,7 +4801,7 @@
       <c r="G47" s="15"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="31"/>
+      <c r="A48" s="34"/>
       <c r="B48" s="15" t="s">
         <v>74</v>
       </c>
@@ -4848,7 +4850,7 @@
       <c r="G50" s="15"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="32">
+      <c r="A51" s="31">
         <v>46101</v>
       </c>
       <c r="B51" s="15" t="s">
@@ -4865,7 +4867,7 @@
       <c r="G51" s="21"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="34"/>
+      <c r="A52" s="32"/>
       <c r="B52" s="15" t="s">
         <v>74</v>
       </c>
@@ -5075,22 +5077,22 @@
   </sheetData>
   <autoFilter ref="A1:F54" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
   <mergeCells count="16">
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="A33:A38"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A29:A31"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:F1001">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -6170,7 +6172,7 @@
       </c>
       <c r="D3" s="3">
         <f>SUM('Nhập xuất tồn'!D3)</f>
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E3" s="3">
         <f>SUM('Nhập xuất tồn'!E3)</f>
@@ -6178,7 +6180,7 @@
       </c>
       <c r="F3" s="3">
         <f>SUM(C3+D3-E3)</f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G3" s="4">
         <f>'Nhập xuất tồn'!G3</f>
@@ -6186,7 +6188,7 @@
       </c>
       <c r="H3" s="3">
         <f>SUM(F3-G3)</f>
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -6657,7 +6659,7 @@
       </c>
       <c r="D19" s="10">
         <f>SUM(D3:D17)</f>
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="E19" s="10">
         <f>SUM(E3:E17)</f>
@@ -6665,7 +6667,7 @@
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
@@ -6673,7 +6675,7 @@
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 03_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B5A0E09-71A6-44B3-A6FE-7DF0C8AC564C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB9F9636-5859-4B4E-8272-FB83B3B1E4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>TungNM:</t>
         </r>
@@ -58,7 +58,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 trả lại kho</t>
@@ -345,9 +345,6 @@
     <t>Đã trả (19/03/26)</t>
   </si>
   <si>
-    <t>Chưa trả</t>
-  </si>
-  <si>
     <t>Đã trả (21/03/26)</t>
   </si>
   <si>
@@ -358,6 +355,9 @@
   </si>
   <si>
     <t>Đã trả (24/03/26)</t>
+  </si>
+  <si>
+    <t>Đã trả (01/04/26)</t>
   </si>
 </sst>
 </file>
@@ -409,14 +409,14 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="E50" s="15"/>
       <c r="F50" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G50" s="15"/>
     </row>
@@ -4862,7 +4862,7 @@
         <v>20</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G51" s="21"/>
     </row>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="E52" s="15"/>
       <c r="F52" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G52" s="21"/>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G53" s="21"/>
     </row>
@@ -4901,7 +4901,7 @@
         <v>46102</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C54" s="15"/>
       <c r="D54" s="15">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="E54" s="15"/>
       <c r="F54" s="15" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G54" s="21"/>
     </row>
@@ -4926,7 +4926,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G55" s="21"/>
     </row>
